--- a/daily/2026-03-30.xlsx
+++ b/daily/2026-03-30.xlsx
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.5</v>
+        <v>20.5</v>
       </c>
       <c r="E2" t="n">
         <v>18.3</v>
@@ -605,13 +605,13 @@
         <v>6.5</v>
       </c>
       <c r="O2" t="n">
+        <v>30</v>
+      </c>
+      <c r="P2" t="n">
         <v>60</v>
       </c>
-      <c r="P2" t="n">
-        <v>73</v>
-      </c>
       <c r="Q2" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="R2" t="n">
         <v>-2.3</v>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="E4" t="n">
         <v>23</v>
@@ -769,13 +769,13 @@
         <v>7.7</v>
       </c>
       <c r="O4" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="P4" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1</v>
+        <v>-2.1</v>
       </c>
       <c r="R4" t="n">
         <v>5.6</v>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="E7" t="n">
         <v>15.3</v>
@@ -1018,10 +1018,10 @@
         <v>90</v>
       </c>
       <c r="P7" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
         <v>3.5</v>
@@ -1530,7 +1530,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Payton Pritchard</t>
+          <t>Onyeka Okongwu</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1540,79 +1540,79 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="n">
-        <v>26</v>
+        <v>11.7</v>
       </c>
       <c r="F14" t="n">
-        <v>21.4</v>
+        <v>9.4</v>
       </c>
       <c r="G14" t="n">
-        <v>18.1</v>
+        <v>10.9</v>
       </c>
       <c r="H14" t="n">
-        <v>16.9</v>
+        <v>13</v>
       </c>
       <c r="I14" t="n">
-        <v>17.8</v>
+        <v>14.1</v>
       </c>
       <c r="J14" t="n">
-        <v>33.6</v>
+        <v>28.8</v>
       </c>
       <c r="K14" t="n">
-        <v>32.6</v>
+        <v>29.9</v>
       </c>
       <c r="L14" t="n">
-        <v>44</v>
+        <v>46.5</v>
       </c>
       <c r="M14" t="n">
-        <v>43.2</v>
+        <v>47.5</v>
       </c>
       <c r="N14" t="n">
-        <v>8.9</v>
+        <v>4.7</v>
       </c>
       <c r="O14" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="P14" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="R14" t="n">
-        <v>3.6</v>
+        <v>-4.7</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8</v>
+        <v>-1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>-1.2</v>
       </c>
       <c r="U14" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>18.4 (5g)</t>
+          <t>16.3 (6g)</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>8.199999999999999</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jayson Tatum</t>
+          <t>Zaccharie Risacher</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1626,75 +1626,75 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>23.5</v>
+        <v>5.5</v>
       </c>
       <c r="E15" t="n">
-        <v>25.7</v>
+        <v>7</v>
       </c>
       <c r="F15" t="n">
-        <v>21.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>21.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>22.6</v>
+        <v>8.5</v>
       </c>
       <c r="I15" t="n">
-        <v>24.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>31.4</v>
+        <v>18.7</v>
       </c>
       <c r="K15" t="n">
-        <v>34.6</v>
+        <v>22</v>
       </c>
       <c r="L15" t="n">
-        <v>39.7</v>
+        <v>52.7</v>
       </c>
       <c r="M15" t="n">
-        <v>42.3</v>
+        <v>45.9</v>
       </c>
       <c r="N15" t="n">
-        <v>5.3</v>
+        <v>6.3</v>
       </c>
       <c r="O15" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="P15" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="R15" t="n">
-        <v>-3.5</v>
+        <v>0.6</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.6</v>
+        <v>6.8</v>
       </c>
       <c r="T15" t="n">
-        <v>-3.2</v>
+        <v>-3.3</v>
       </c>
       <c r="U15" t="n">
+        <v>2</v>
+      </c>
+      <c r="V15" t="n">
         <v>24</v>
       </c>
-      <c r="V15" t="n">
-        <v>5</v>
-      </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>24.2 (4g)</t>
+          <t>9.7 (3g)</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>-6</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Dyson Daniels</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1704,79 +1704,79 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>10.5</v>
       </c>
       <c r="E16" t="n">
-        <v>11.7</v>
+        <v>11.3</v>
       </c>
       <c r="F16" t="n">
-        <v>10.2</v>
+        <v>13</v>
       </c>
       <c r="G16" t="n">
-        <v>9.699999999999999</v>
+        <v>13.6</v>
       </c>
       <c r="H16" t="n">
-        <v>10.2</v>
+        <v>12.5</v>
       </c>
       <c r="I16" t="n">
-        <v>9.5</v>
+        <v>11.6</v>
       </c>
       <c r="J16" t="n">
-        <v>26.9</v>
+        <v>32.4</v>
       </c>
       <c r="K16" t="n">
-        <v>25.9</v>
+        <v>31.7</v>
       </c>
       <c r="L16" t="n">
-        <v>62.3</v>
+        <v>55.8</v>
       </c>
       <c r="M16" t="n">
-        <v>61.2</v>
+        <v>52.1</v>
       </c>
       <c r="N16" t="n">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="O16" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="P16" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1</v>
+        <v>1.1</v>
       </c>
       <c r="R16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T16" t="n">
         <v>0.7</v>
       </c>
-      <c r="S16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
       <c r="U16" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="V16" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>6.2 (5g)</t>
+          <t>16.0 (5g)</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Derrick White</t>
+          <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1793,72 +1793,72 @@
         <v>17.5</v>
       </c>
       <c r="E17" t="n">
-        <v>12.3</v>
+        <v>22.7</v>
       </c>
       <c r="F17" t="n">
-        <v>12.4</v>
+        <v>22.2</v>
       </c>
       <c r="G17" t="n">
-        <v>15.8</v>
+        <v>23.3</v>
       </c>
       <c r="H17" t="n">
-        <v>16.5</v>
+        <v>21.2</v>
       </c>
       <c r="I17" t="n">
-        <v>15.8</v>
+        <v>20.6</v>
       </c>
       <c r="J17" t="n">
-        <v>34.1</v>
+        <v>33.2</v>
       </c>
       <c r="K17" t="n">
-        <v>34.4</v>
+        <v>33.8</v>
       </c>
       <c r="L17" t="n">
-        <v>38</v>
+        <v>51.6</v>
       </c>
       <c r="M17" t="n">
-        <v>38</v>
+        <v>45.3</v>
       </c>
       <c r="N17" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="O17" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="P17" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.7</v>
+        <v>3.1</v>
       </c>
       <c r="R17" t="n">
-        <v>-3.4</v>
+        <v>1.6</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3</v>
+        <v>-0.6</v>
       </c>
       <c r="U17" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="V17" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>16.8 (6g)</t>
+          <t>13.4 (5g)</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1.1</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Jalen Johnson</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1868,79 +1868,79 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>27.5</v>
+        <v>21.5</v>
       </c>
       <c r="E18" t="n">
-        <v>30</v>
+        <v>27.3</v>
       </c>
       <c r="F18" t="n">
-        <v>32.6</v>
+        <v>22.6</v>
       </c>
       <c r="G18" t="n">
-        <v>26.8</v>
+        <v>24.3</v>
       </c>
       <c r="H18" t="n">
-        <v>26.6</v>
+        <v>22.6</v>
       </c>
       <c r="I18" t="n">
-        <v>27.4</v>
+        <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>34.4</v>
+        <v>37</v>
       </c>
       <c r="K18" t="n">
-        <v>34.6</v>
+        <v>35.3</v>
       </c>
       <c r="L18" t="n">
-        <v>46.6</v>
+        <v>50</v>
       </c>
       <c r="M18" t="n">
-        <v>46.3</v>
+        <v>45.5</v>
       </c>
       <c r="N18" t="n">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="O18" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="P18" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1</v>
+        <v>0.5</v>
       </c>
       <c r="R18" t="n">
-        <v>5.2</v>
+        <v>0.6</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3</v>
+        <v>4.5</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2</v>
+        <v>1.7</v>
       </c>
       <c r="U18" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>30.8 (4g)</t>
+          <t>18.7 (6g)</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>-2.1</v>
+        <v>-7.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Onyeka Okongwu</t>
+          <t>CJ McCollum</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1950,59 +1950,59 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="E19" t="n">
-        <v>11.7</v>
+        <v>23.3</v>
       </c>
       <c r="F19" t="n">
-        <v>9.4</v>
+        <v>21.6</v>
       </c>
       <c r="G19" t="n">
-        <v>10.9</v>
+        <v>20.2</v>
       </c>
       <c r="H19" t="n">
-        <v>13</v>
+        <v>18.9</v>
       </c>
       <c r="I19" t="n">
-        <v>14.1</v>
+        <v>19.2</v>
       </c>
       <c r="J19" t="n">
-        <v>28.8</v>
+        <v>29.2</v>
       </c>
       <c r="K19" t="n">
-        <v>29.9</v>
+        <v>28.9</v>
       </c>
       <c r="L19" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="M19" t="n">
         <v>46.5</v>
       </c>
-      <c r="M19" t="n">
-        <v>47.5</v>
-      </c>
       <c r="N19" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="O19" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P19" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="R19" t="n">
-        <v>-4.7</v>
+        <v>2.4</v>
       </c>
       <c r="S19" t="n">
-        <v>-1</v>
+        <v>2.4</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2</v>
+        <v>0.2</v>
       </c>
       <c r="U19" t="n">
         <v>2</v>
@@ -2012,17 +2012,17 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>16.3 (6g)</t>
+          <t>14.3 (7g)</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>5.9</v>
+        <v>-10.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Zaccharie Risacher</t>
+          <t>Jonathan Kuminga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2036,55 +2036,55 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="E20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F20" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="G20" t="n">
-        <v>9.800000000000001</v>
+        <v>11.8</v>
       </c>
       <c r="H20" t="n">
-        <v>8.5</v>
+        <v>9.9</v>
       </c>
       <c r="I20" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="J20" t="n">
-        <v>18.7</v>
+        <v>21.5</v>
       </c>
       <c r="K20" t="n">
-        <v>22</v>
+        <v>23.1</v>
       </c>
       <c r="L20" t="n">
-        <v>52.7</v>
+        <v>40.9</v>
       </c>
       <c r="M20" t="n">
-        <v>45.9</v>
+        <v>43.4</v>
       </c>
       <c r="N20" t="n">
-        <v>6.3</v>
+        <v>8.6</v>
       </c>
       <c r="O20" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="P20" t="n">
         <v>70</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6</v>
+        <v>-3</v>
       </c>
       <c r="S20" t="n">
-        <v>6.8</v>
+        <v>-2.5</v>
       </c>
       <c r="T20" t="n">
-        <v>-3.3</v>
+        <v>-1.6</v>
       </c>
       <c r="U20" t="n">
         <v>2</v>
@@ -2092,19 +2092,15 @@
       <c r="V20" t="n">
         <v>24</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>9.7 (3g)</t>
-        </is>
-      </c>
+      <c r="W20" t="inlineStr"/>
       <c r="X20" t="n">
-        <v>-12</v>
+        <v>-13.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sam Hauser</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2114,79 +2110,79 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8.5</v>
+        <v>27.5</v>
       </c>
       <c r="E21" t="n">
-        <v>8.699999999999999</v>
+        <v>30</v>
       </c>
       <c r="F21" t="n">
-        <v>5.6</v>
+        <v>32.6</v>
       </c>
       <c r="G21" t="n">
-        <v>6.7</v>
+        <v>26.8</v>
       </c>
       <c r="H21" t="n">
-        <v>8.5</v>
+        <v>26.6</v>
       </c>
       <c r="I21" t="n">
-        <v>9.199999999999999</v>
+        <v>27.4</v>
       </c>
       <c r="J21" t="n">
-        <v>26.2</v>
+        <v>34.4</v>
       </c>
       <c r="K21" t="n">
-        <v>27.2</v>
+        <v>34.6</v>
       </c>
       <c r="L21" t="n">
-        <v>33.8</v>
+        <v>46.6</v>
       </c>
       <c r="M21" t="n">
-        <v>38.9</v>
+        <v>46.3</v>
       </c>
       <c r="N21" t="n">
-        <v>4.1</v>
+        <v>9.5</v>
       </c>
       <c r="O21" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="P21" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.7</v>
+        <v>-0.1</v>
       </c>
       <c r="R21" t="n">
-        <v>-3.6</v>
+        <v>5.2</v>
       </c>
       <c r="S21" t="n">
-        <v>-5.1</v>
+        <v>0.3</v>
       </c>
       <c r="T21" t="n">
-        <v>-1</v>
+        <v>-0.2</v>
       </c>
       <c r="U21" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="V21" t="n">
         <v>5</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>11.3 (6g)</t>
+          <t>30.8 (4g)</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>0.6</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Dyson Daniels</t>
+          <t>Payton Pritchard</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2200,75 +2196,75 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10.5</v>
+        <v>18.5</v>
       </c>
       <c r="E22" t="n">
-        <v>11.3</v>
+        <v>26</v>
       </c>
       <c r="F22" t="n">
-        <v>13</v>
+        <v>21.4</v>
       </c>
       <c r="G22" t="n">
-        <v>13.6</v>
+        <v>18.1</v>
       </c>
       <c r="H22" t="n">
-        <v>12.5</v>
+        <v>16.9</v>
       </c>
       <c r="I22" t="n">
-        <v>11.6</v>
+        <v>17.8</v>
       </c>
       <c r="J22" t="n">
-        <v>32.4</v>
+        <v>33.6</v>
       </c>
       <c r="K22" t="n">
-        <v>31.7</v>
+        <v>32.6</v>
       </c>
       <c r="L22" t="n">
-        <v>55.8</v>
+        <v>44</v>
       </c>
       <c r="M22" t="n">
-        <v>52.1</v>
+        <v>43.2</v>
       </c>
       <c r="N22" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
       <c r="O22" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="P22" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.1</v>
+        <v>-0.7</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="S22" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="T22" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="V22" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>16.0 (5g)</t>
+          <t>18.4 (5g)</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nickeil Alexander-Walker</t>
+          <t>Derrick White</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2285,72 +2281,72 @@
         <v>17.5</v>
       </c>
       <c r="E23" t="n">
-        <v>22.7</v>
+        <v>12.3</v>
       </c>
       <c r="F23" t="n">
-        <v>22.2</v>
+        <v>12.4</v>
       </c>
       <c r="G23" t="n">
-        <v>23.3</v>
+        <v>15.8</v>
       </c>
       <c r="H23" t="n">
-        <v>21.2</v>
+        <v>16.5</v>
       </c>
       <c r="I23" t="n">
-        <v>20.6</v>
+        <v>15.8</v>
       </c>
       <c r="J23" t="n">
-        <v>33.2</v>
+        <v>34.1</v>
       </c>
       <c r="K23" t="n">
-        <v>33.8</v>
+        <v>34.4</v>
       </c>
       <c r="L23" t="n">
-        <v>51.6</v>
+        <v>38</v>
       </c>
       <c r="M23" t="n">
-        <v>45.3</v>
+        <v>38</v>
       </c>
       <c r="N23" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="O23" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="P23" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.1</v>
+        <v>-1.7</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6</v>
+        <v>-3.4</v>
       </c>
       <c r="S23" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="U23" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="V23" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>13.4 (5g)</t>
+          <t>16.8 (6g)</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>-2.8</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Sam Hauser</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2364,75 +2360,75 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>21.5</v>
+        <v>8.5</v>
       </c>
       <c r="E24" t="n">
-        <v>27.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>22.6</v>
+        <v>5.6</v>
       </c>
       <c r="G24" t="n">
-        <v>24.3</v>
+        <v>6.7</v>
       </c>
       <c r="H24" t="n">
-        <v>22.6</v>
+        <v>8.5</v>
       </c>
       <c r="I24" t="n">
-        <v>22</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>37</v>
+        <v>26.2</v>
       </c>
       <c r="K24" t="n">
-        <v>35.3</v>
+        <v>27.2</v>
       </c>
       <c r="L24" t="n">
-        <v>50</v>
+        <v>33.8</v>
       </c>
       <c r="M24" t="n">
-        <v>45.5</v>
+        <v>38.9</v>
       </c>
       <c r="N24" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="O24" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="P24" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="R24" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>24</v>
+      </c>
+      <c r="V24" t="n">
+        <v>5</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>11.3 (6g)</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
         <v>0.6</v>
-      </c>
-      <c r="S24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2</v>
-      </c>
-      <c r="V24" t="n">
-        <v>24</v>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>18.7 (6g)</t>
-        </is>
-      </c>
-      <c r="X24" t="n">
-        <v>-7.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CJ McCollum</t>
+          <t>Jayson Tatum</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2442,79 +2438,79 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>17.5</v>
+        <v>20.5</v>
       </c>
       <c r="E25" t="n">
-        <v>23.3</v>
+        <v>25.7</v>
       </c>
       <c r="F25" t="n">
-        <v>21.6</v>
+        <v>21.2</v>
       </c>
       <c r="G25" t="n">
-        <v>20.2</v>
+        <v>21.5</v>
       </c>
       <c r="H25" t="n">
-        <v>18.9</v>
+        <v>22.6</v>
       </c>
       <c r="I25" t="n">
-        <v>19.2</v>
+        <v>24.7</v>
       </c>
       <c r="J25" t="n">
-        <v>29.2</v>
+        <v>31.4</v>
       </c>
       <c r="K25" t="n">
-        <v>28.9</v>
+        <v>34.6</v>
       </c>
       <c r="L25" t="n">
-        <v>48.9</v>
+        <v>39.7</v>
       </c>
       <c r="M25" t="n">
-        <v>46.5</v>
+        <v>42.3</v>
       </c>
       <c r="N25" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="O25" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="P25" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="R25" t="n">
-        <v>2.4</v>
+        <v>-3.5</v>
       </c>
       <c r="S25" t="n">
-        <v>2.4</v>
+        <v>-2.6</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2</v>
+        <v>-3.2</v>
       </c>
       <c r="U25" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="V25" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>14.3 (7g)</t>
+          <t>24.2 (4g)</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>-10.6</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jonathan Kuminga</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2524,69 +2520,73 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="E26" t="n">
-        <v>9</v>
+        <v>11.7</v>
       </c>
       <c r="F26" t="n">
-        <v>9</v>
+        <v>10.2</v>
       </c>
       <c r="G26" t="n">
-        <v>11.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>9.9</v>
+        <v>10.2</v>
       </c>
       <c r="I26" t="n">
-        <v>12</v>
+        <v>9.5</v>
       </c>
       <c r="J26" t="n">
-        <v>21.5</v>
+        <v>26.9</v>
       </c>
       <c r="K26" t="n">
-        <v>23.1</v>
+        <v>25.9</v>
       </c>
       <c r="L26" t="n">
-        <v>40.9</v>
+        <v>62.3</v>
       </c>
       <c r="M26" t="n">
-        <v>43.4</v>
+        <v>61.2</v>
       </c>
       <c r="N26" t="n">
-        <v>8.6</v>
+        <v>6.7</v>
       </c>
       <c r="O26" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="P26" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>-3</v>
+        <v>0.7</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.5</v>
+        <v>1.1</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.6</v>
+        <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="V26" t="n">
-        <v>24</v>
-      </c>
-      <c r="W26" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>6.2 (5g)</t>
+        </is>
+      </c>
       <c r="X26" t="n">
-        <v>-13.9</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="27">
@@ -3154,7 +3154,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Luke Kornet</t>
+          <t>Collin Sexton</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3164,79 +3164,79 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>5.5</v>
+        <v>16.5</v>
       </c>
       <c r="E34" t="n">
-        <v>5.3</v>
+        <v>21.3</v>
       </c>
       <c r="F34" t="n">
-        <v>4.2</v>
+        <v>19.6</v>
       </c>
       <c r="G34" t="n">
-        <v>4.7</v>
+        <v>21.2</v>
       </c>
       <c r="H34" t="n">
-        <v>4.5</v>
+        <v>16.6</v>
       </c>
       <c r="I34" t="n">
-        <v>4.7</v>
+        <v>14.9</v>
       </c>
       <c r="J34" t="n">
-        <v>19</v>
+        <v>26.3</v>
       </c>
       <c r="K34" t="n">
-        <v>17.2</v>
+        <v>22</v>
       </c>
       <c r="L34" t="n">
-        <v>47.2</v>
+        <v>52.3</v>
       </c>
       <c r="M34" t="n">
-        <v>56.8</v>
+        <v>49.3</v>
       </c>
       <c r="N34" t="n">
-        <v>3.7</v>
+        <v>6.6</v>
       </c>
       <c r="O34" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="P34" t="n">
         <v>40</v>
       </c>
       <c r="Q34" t="n">
-        <v>-0.8</v>
+        <v>-1.6</v>
       </c>
       <c r="R34" t="n">
-        <v>-0.5</v>
+        <v>4.7</v>
       </c>
       <c r="S34" t="n">
-        <v>-9.6</v>
+        <v>3</v>
       </c>
       <c r="T34" t="n">
-        <v>1.8</v>
+        <v>4.3</v>
       </c>
       <c r="U34" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="V34" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>5.5 (4g)</t>
+          <t>19.6 (5g)</t>
         </is>
       </c>
       <c r="X34" t="n">
-        <v>-3.9</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Collin Sexton</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3250,75 +3250,75 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="E35" t="n">
-        <v>21.3</v>
+        <v>18.7</v>
       </c>
       <c r="F35" t="n">
-        <v>19.6</v>
+        <v>16.4</v>
       </c>
       <c r="G35" t="n">
-        <v>21.2</v>
+        <v>17.4</v>
       </c>
       <c r="H35" t="n">
-        <v>16.6</v>
+        <v>15.5</v>
       </c>
       <c r="I35" t="n">
-        <v>14.9</v>
+        <v>15.8</v>
       </c>
       <c r="J35" t="n">
-        <v>26.3</v>
+        <v>29.3</v>
       </c>
       <c r="K35" t="n">
-        <v>22</v>
+        <v>28.3</v>
       </c>
       <c r="L35" t="n">
-        <v>52.3</v>
+        <v>46.8</v>
       </c>
       <c r="M35" t="n">
-        <v>49.3</v>
+        <v>48.3</v>
       </c>
       <c r="N35" t="n">
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
       <c r="O35" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="P35" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="Q35" t="n">
-        <v>-1.6</v>
+        <v>0.3</v>
       </c>
       <c r="R35" t="n">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>-1.5</v>
       </c>
       <c r="T35" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="V35" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>19.6 (5g)</t>
+          <t>13.7 (3g)</t>
         </is>
       </c>
       <c r="X35" t="n">
-        <v>7.6</v>
+        <v>-4.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Isaac Okoro</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3328,79 +3328,79 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>15.5</v>
+        <v>8.5</v>
       </c>
       <c r="E36" t="n">
-        <v>18.7</v>
+        <v>13.3</v>
       </c>
       <c r="F36" t="n">
-        <v>16.4</v>
+        <v>11</v>
       </c>
       <c r="G36" t="n">
-        <v>17.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>15.5</v>
+        <v>10.6</v>
       </c>
       <c r="I36" t="n">
-        <v>15.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>29.3</v>
+        <v>30.5</v>
       </c>
       <c r="K36" t="n">
-        <v>28.3</v>
+        <v>29.2</v>
       </c>
       <c r="L36" t="n">
-        <v>46.8</v>
+        <v>38.7</v>
       </c>
       <c r="M36" t="n">
-        <v>48.3</v>
+        <v>42.8</v>
       </c>
       <c r="N36" t="n">
-        <v>8.1</v>
+        <v>4.7</v>
       </c>
       <c r="O36" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="P36" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="R36" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="S36" t="n">
-        <v>-1.5</v>
+        <v>-4.1</v>
       </c>
       <c r="T36" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="U36" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="V36" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>13.7 (3g)</t>
+          <t>5.7 (3g)</t>
         </is>
       </c>
       <c r="X36" t="n">
-        <v>-4.6</v>
+        <v>-11.9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Isaac Okoro</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3414,75 +3414,71 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>8.5</v>
+        <v>26.5</v>
       </c>
       <c r="E37" t="n">
-        <v>13.3</v>
+        <v>22.7</v>
       </c>
       <c r="F37" t="n">
-        <v>11</v>
+        <v>24.4</v>
       </c>
       <c r="G37" t="n">
-        <v>9.699999999999999</v>
+        <v>26.1</v>
       </c>
       <c r="H37" t="n">
-        <v>10.6</v>
+        <v>23.9</v>
       </c>
       <c r="I37" t="n">
-        <v>9.800000000000001</v>
+        <v>23.6</v>
       </c>
       <c r="J37" t="n">
-        <v>30.5</v>
+        <v>29.9</v>
       </c>
       <c r="K37" t="n">
-        <v>29.2</v>
+        <v>29.8</v>
       </c>
       <c r="L37" t="n">
-        <v>38.7</v>
+        <v>50.4</v>
       </c>
       <c r="M37" t="n">
-        <v>42.8</v>
+        <v>48.7</v>
       </c>
       <c r="N37" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="O37" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="P37" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.3</v>
+        <v>-2.9</v>
       </c>
       <c r="R37" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="S37" t="n">
-        <v>-4.1</v>
+        <v>1.7</v>
       </c>
       <c r="T37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="V37" t="n">
-        <v>9</v>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>5.7 (3g)</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="W37" t="inlineStr"/>
       <c r="X37" t="n">
-        <v>-11.9</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Keldon Johnson</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3496,55 +3492,55 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>26.5</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="n">
-        <v>22.7</v>
+        <v>17.3</v>
       </c>
       <c r="F38" t="n">
-        <v>24.4</v>
+        <v>16.4</v>
       </c>
       <c r="G38" t="n">
-        <v>26.1</v>
+        <v>13.4</v>
       </c>
       <c r="H38" t="n">
-        <v>23.9</v>
+        <v>11.8</v>
       </c>
       <c r="I38" t="n">
-        <v>23.6</v>
+        <v>12.7</v>
       </c>
       <c r="J38" t="n">
-        <v>29.9</v>
+        <v>22.4</v>
       </c>
       <c r="K38" t="n">
-        <v>29.8</v>
+        <v>22.3</v>
       </c>
       <c r="L38" t="n">
-        <v>50.4</v>
+        <v>51.5</v>
       </c>
       <c r="M38" t="n">
-        <v>48.7</v>
+        <v>48.3</v>
       </c>
       <c r="N38" t="n">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="O38" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="P38" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="Q38" t="n">
-        <v>-2.9</v>
+        <v>0.2</v>
       </c>
       <c r="R38" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="S38" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="U38" t="n">
         <v>28</v>
@@ -3552,15 +3548,19 @@
       <c r="V38" t="n">
         <v>2</v>
       </c>
-      <c r="W38" t="inlineStr"/>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>16.3 (3g)</t>
+        </is>
+      </c>
       <c r="X38" t="n">
-        <v>5.7</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Keldon Johnson</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3570,79 +3570,75 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="E39" t="n">
-        <v>17.3</v>
+        <v>15</v>
       </c>
       <c r="F39" t="n">
-        <v>16.4</v>
+        <v>14.8</v>
       </c>
       <c r="G39" t="n">
-        <v>13.4</v>
+        <v>13.8</v>
       </c>
       <c r="H39" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="I39" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="J39" t="n">
-        <v>22.4</v>
+        <v>23.9</v>
       </c>
       <c r="K39" t="n">
-        <v>22.3</v>
+        <v>23.3</v>
       </c>
       <c r="L39" t="n">
-        <v>51.5</v>
+        <v>58.1</v>
       </c>
       <c r="M39" t="n">
-        <v>48.3</v>
+        <v>56.2</v>
       </c>
       <c r="N39" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="O39" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="P39" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.2</v>
+        <v>-0.9</v>
       </c>
       <c r="R39" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="S39" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="T39" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="U39" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="V39" t="n">
         <v>2</v>
       </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>16.3 (3g)</t>
-        </is>
-      </c>
+      <c r="W39" t="inlineStr"/>
       <c r="X39" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Matas Buzelis</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3652,75 +3648,79 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="E40" t="n">
-        <v>15</v>
+        <v>20.7</v>
       </c>
       <c r="F40" t="n">
-        <v>14.8</v>
+        <v>19.6</v>
       </c>
       <c r="G40" t="n">
-        <v>13.8</v>
+        <v>22.7</v>
       </c>
       <c r="H40" t="n">
-        <v>13.2</v>
+        <v>19.9</v>
       </c>
       <c r="I40" t="n">
-        <v>12.6</v>
+        <v>18.5</v>
       </c>
       <c r="J40" t="n">
-        <v>23.9</v>
+        <v>34.8</v>
       </c>
       <c r="K40" t="n">
-        <v>23.3</v>
+        <v>31.4</v>
       </c>
       <c r="L40" t="n">
-        <v>58.1</v>
+        <v>44.4</v>
       </c>
       <c r="M40" t="n">
-        <v>56.2</v>
+        <v>43.7</v>
       </c>
       <c r="N40" t="n">
-        <v>6.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O40" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="P40" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="Q40" t="n">
-        <v>-0.9</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="S40" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="T40" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="U40" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="V40" t="n">
-        <v>2</v>
-      </c>
-      <c r="W40" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>8.7 (3g)</t>
+        </is>
+      </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Matas Buzelis</t>
+          <t>Luke Kornet</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3730,73 +3730,73 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>18.5</v>
+        <v>3.5</v>
       </c>
       <c r="E41" t="n">
-        <v>20.7</v>
+        <v>5.3</v>
       </c>
       <c r="F41" t="n">
-        <v>19.6</v>
+        <v>4.2</v>
       </c>
       <c r="G41" t="n">
-        <v>22.7</v>
+        <v>4.7</v>
       </c>
       <c r="H41" t="n">
-        <v>19.9</v>
+        <v>4.5</v>
       </c>
       <c r="I41" t="n">
-        <v>18.5</v>
+        <v>4.7</v>
       </c>
       <c r="J41" t="n">
-        <v>34.8</v>
+        <v>19</v>
       </c>
       <c r="K41" t="n">
-        <v>31.4</v>
+        <v>17.2</v>
       </c>
       <c r="L41" t="n">
-        <v>44.4</v>
+        <v>47.2</v>
       </c>
       <c r="M41" t="n">
-        <v>43.7</v>
+        <v>56.8</v>
       </c>
       <c r="N41" t="n">
-        <v>8.300000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="O41" t="n">
         <v>60</v>
       </c>
       <c r="P41" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="Q41" t="n">
-        <v>-0</v>
+        <v>1.2</v>
       </c>
       <c r="R41" t="n">
-        <v>1.1</v>
+        <v>-0.5</v>
       </c>
       <c r="S41" t="n">
-        <v>0.7</v>
+        <v>-9.6</v>
       </c>
       <c r="T41" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="U41" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="V41" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>8.7 (3g)</t>
+          <t>5.5 (4g)</t>
         </is>
       </c>
       <c r="X41" t="n">
-        <v>4.3</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="42">
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="n">
         <v>9</v>
@@ -3849,13 +3849,13 @@
         <v>8.1</v>
       </c>
       <c r="O42" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="P42" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="R42" t="n">
         <v>1.1</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="E44" t="n">
         <v>9.699999999999999</v>
@@ -4019,7 +4019,7 @@
         <v>33</v>
       </c>
       <c r="Q44" t="n">
-        <v>-0.5</v>
+        <v>-1.5</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4136,7 +4136,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="E46" t="n">
         <v>17.7</v>
@@ -4172,10 +4172,10 @@
         <v>50</v>
       </c>
       <c r="P46" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R46" t="n">
         <v>-1.5</v>
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>20.5</v>
+        <v>22.5</v>
       </c>
       <c r="E51" t="n">
         <v>24</v>
@@ -4567,13 +4567,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="O51" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="P51" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="Q51" t="n">
-        <v>-3.5</v>
+        <v>-5.5</v>
       </c>
       <c r="R51" t="n">
         <v>5.6</v>
@@ -4616,7 +4616,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
       <c r="E52" t="n">
         <v>24.3</v>
@@ -4649,13 +4649,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="O52" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="P52" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.1</v>
+        <v>-0.9</v>
       </c>
       <c r="R52" t="n">
         <v>-3.8</v>
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="E74" t="n">
         <v>8</v>
@@ -6445,13 +6445,13 @@
         <v>3</v>
       </c>
       <c r="O74" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="P74" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="Q74" t="n">
-        <v>-0.4</v>
+        <v>-1.4</v>
       </c>
       <c r="R74" t="n">
         <v>0.9</v>
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="E75" t="n">
         <v>19</v>
@@ -6526,10 +6526,10 @@
         <v>60</v>
       </c>
       <c r="P75" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.6</v>
+        <v>-0.4</v>
       </c>
       <c r="R75" t="n">
         <v>3.9</v>
@@ -6654,7 +6654,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="E77" t="n">
         <v>9.699999999999999</v>
@@ -6690,10 +6690,10 @@
         <v>50</v>
       </c>
       <c r="P77" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Q77" t="n">
-        <v>-1.2</v>
+        <v>-2.2</v>
       </c>
       <c r="R77" t="n">
         <v>1.5</v>
@@ -7692,7 +7692,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="n">
         <v>8.699999999999999</v>
@@ -7731,7 +7731,7 @@
         <v>17</v>
       </c>
       <c r="Q90" t="n">
-        <v>-4.9</v>
+        <v>-3.9</v>
       </c>
       <c r="R90" t="n">
         <v>1.2</v>
@@ -8488,7 +8488,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="E100" t="n">
         <v>5.7</v>
@@ -8521,13 +8521,13 @@
         <v>3.9</v>
       </c>
       <c r="O100" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="P100" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="Q100" t="n">
-        <v>-3.5</v>
+        <v>-2.5</v>
       </c>
       <c r="R100" t="n">
         <v>-3.8</v>
@@ -8818,10 +8818,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.553</v>
+        <v>0.597</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -8830,17 +8830,17 @@
         <v>17</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
-        <v>1.917</v>
+        <v>1.952</v>
       </c>
       <c r="K2" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 2.3 pts (L5 vs L30) — marginally supports the UNDER. TS% shifts +17.8% in this matchup. Opponent is below-average defense (#16) at slow pace (#23). Mixed signals: 4/10 agree (Trend, Pace, FG Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 17.0 pts (1.5 pts below line; 55% blended confidence [T3]). Risk: 73% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
+          <t>Recent scoring trending down 2.3 pts (L5 vs L30) — supports the UNDER. TS% shifts +17.8% in this matchup. Opponent is below-average defense (#16) at slow pace (#23). 7/10 signals agree — HR L10, Trend, Context, H2H support the UNDER; Volume, HR L30, Defense dissent. Projection model targets 17.0 pts (3.5 pts below line; 59% blended confidence [T3]). Risk: 60% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
         </is>
       </c>
     </row>
@@ -8881,10 +8881,10 @@
         <v>1.5</v>
       </c>
       <c r="J3" t="n">
+        <v>1.952</v>
+      </c>
+      <c r="K3" t="n">
         <v>1.8</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1.971</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.655</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
@@ -8926,17 +8926,17 @@
         <v>11.1</v>
       </c>
       <c r="I4" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="J4" t="n">
-        <v>1.971</v>
+        <v>1.833</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8</v>
+        <v>1.901</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>George averages 12.3 pts in 3 meetings (-5.2 vs line) — marginally supports the UNDER. H2H avg 4.1 pts below season L30; TS% shifts -7.7% in this matchup. Opponent is weak defense (#23) at fast pace (#4). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, Pace. Projection model targets 11.1 pts (6.4 pts below line; 65% blended confidence [T3]). Risk: L3 has surged to 23.0 after a 35-pt outing (6.6 above L30) — momentum could push over the under line.</t>
+          <t>George averages 12.3 pts in 3 meetings (-6.2 vs line) — marginally supports the UNDER. H2H avg 4.1 pts below season L30; TS% shifts -7.7% in this matchup. Opponent is weak defense (#23) at fast pace (#4). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, Pace. Projection model targets 11.1 pts (7.4 pts below line; 68% blended confidence [T3]). Risk: L3 has surged to 23.0 after a 35-pt outing (6.6 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
@@ -8977,10 +8977,10 @@
         <v>1.6</v>
       </c>
       <c r="J5" t="n">
-        <v>1.901</v>
+        <v>1.8</v>
       </c>
       <c r="K5" t="n">
-        <v>1.862</v>
+        <v>1.952</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
@@ -9025,10 +9025,10 @@
         <v>0.9</v>
       </c>
       <c r="J6" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="K6" t="n">
-        <v>1.893</v>
+        <v>1.952</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.729</v>
+        <v>0.698</v>
       </c>
       <c r="F7" t="n">
         <v>9</v>
@@ -9070,17 +9070,17 @@
         <v>14.6</v>
       </c>
       <c r="I7" t="n">
-        <v>6.1</v>
+        <v>5.1</v>
       </c>
       <c r="J7" t="n">
-        <v>1.787</v>
+        <v>1.952</v>
       </c>
       <c r="K7" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Grimes averages 14.4 pts in 5 meetings (+5.9 vs line) — supports the OVER. TS% shifts -7.6% in this matchup; Minutes up 4.8 recently (L10=33.0 vs L30=28.2). Opponent is below-average defense (#22) at fast pace (#4). 9/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; FG Trend dissents. Projection model targets 14.6 pts (6.1 pts above line; 72% blended confidence [T3]). Risk: high variance (σ=8.0) makes the outcome difficult to call with confidence.</t>
+          <t>Grimes averages 14.4 pts in 5 meetings (+4.9 vs line) — supports the OVER. TS% shifts -7.6% in this matchup; Minutes up 4.8 recently (L10=33.0 vs L30=28.2). Opponent is below-average defense (#22) at fast pace (#4). 9/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; FG Trend dissents. Projection model targets 14.6 pts (5.1 pts above line; 69% blended confidence [T3]). Risk: high variance (σ=8.0) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
@@ -9121,10 +9121,10 @@
         <v>4.1</v>
       </c>
       <c r="J8" t="n">
-        <v>1.719</v>
+        <v>1.758</v>
       </c>
       <c r="K8" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
@@ -9169,10 +9169,10 @@
         <v>5.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1.909</v>
+        <v>1.87</v>
       </c>
       <c r="K9" t="n">
-        <v>1.847</v>
+        <v>1.87</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
@@ -9217,10 +9217,10 @@
         <v>3.4</v>
       </c>
       <c r="J10" t="n">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="K10" t="n">
-        <v>1.781</v>
+        <v>1.87</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
@@ -9265,10 +9265,10 @@
         <v>6.8</v>
       </c>
       <c r="J11" t="n">
-        <v>1.84</v>
+        <v>1.952</v>
       </c>
       <c r="K11" t="n">
-        <v>1.917</v>
+        <v>1.8</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
@@ -9313,10 +9313,10 @@
         <v>1.7</v>
       </c>
       <c r="J12" t="n">
-        <v>1.877</v>
+        <v>1.952</v>
       </c>
       <c r="K12" t="n">
-        <v>1.877</v>
+        <v>1.8</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
@@ -9361,10 +9361,10 @@
         <v>0.8</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>1.833</v>
       </c>
       <c r="K13" t="n">
-        <v>1.769</v>
+        <v>1.909</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Payton Pritchard</t>
+          <t>Onyeka Okongwu</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -9394,36 +9394,36 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.614</v>
+        <v>0.539</v>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>21.5</v>
+        <v>13.7</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J14" t="n">
-        <v>1.826</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>1.909</v>
+        <v>1.364</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 3.6 pts (L5 vs L30) — supports the OVER. TS% shifts +8.2% in this matchup. Opponent is below-average defense (#20) at fast pace (#5). Full consensus: 10/10 signals aligned (Volume, HR L30, HR L10, Trend). Projection model targets 21.5 pts (4.0 pts above line; 61% blended confidence [T3]). Risk: high variance (σ=8.9) makes the outcome difficult to call with confidence.</t>
+          <t>Okongwu averages 16.3 pts in 6 meetings (+3.8 vs line) — marginally supports the OVER. H2H avg 2.2 pts above season L30; TS% shifts +5.9% in this matchup. Opponent is elite defense (#2) at slow pace (#24). Mixed signals: 4/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 13.7 pts (1.2 pts above line; 53% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jayson Tatum</t>
+          <t>Zaccharie Risacher</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9442,36 +9442,36 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.55</v>
+        <v>0.554</v>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>21.6</v>
+        <v>6.2</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J15" t="n">
-        <v>1.87</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>1.87</v>
+        <v>1.364</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 3.5 pts (L5 vs L30) — marginally supports the UNDER. TS% shifts -6.0% in this matchup; Minutes down 3.2 recently (L10=31.4 vs L30=34.6). Opponent is weak defense (#24) at fast pace (#5). Mixed signals: 4/10 agree (HR L10, Trend, FG Trend); counter-signals: Volume, HR L30, Context. Projection model targets 21.6 pts (1.9 pts below line; 54% blended confidence [T3]). Risk: minutes trending down (31.4 L10 vs 34.6 L30) — role reduction would suppress counting stats.</t>
+          <t>Risacher averages 9.7 pts in 3 meetings (+4.2 vs line) — supports the OVER. TS% shifts -12.0% in this matchup; FG% +6.8% trending (L10 vs L30). Opponent is elite defense (#2) at slow pace (#24). 7/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; Defense, Pace, Min Trend dissent. Projection model targets 6.2 pts (0.7 pts above line; 55% blended confidence [T3]). Risk: minutes trending down (18.7 L10 vs 22.0 L30) — role reduction would suppress counting stats.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Dyson Daniels</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -9481,45 +9481,45 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.569</v>
+        <v>0.625</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>8.1</v>
+        <v>14.8</v>
       </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="J16" t="n">
-        <v>1.833</v>
+        <v>2.9</v>
       </c>
       <c r="K16" t="n">
-        <v>1.893</v>
+        <v>1.385</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Queta averages 6.2 pts in 5 meetings (-4.3 vs line) — marginally supports the UNDER. H2H avg 3.3 pts below season L30; TS% shifts +6.7% in this matchup. Opponent is below-average defense (#17) at fast pace (#5). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, Pace. Projection model targets 8.1 pts (2.4 pts below line; 56% blended confidence [T3]).</t>
+          <t>Daniels averages 16.0 pts in 5 meetings (+5.5 vs line) — supports the OVER. H2H avg 4.4 pts above season L30; TS% shifts +7.2% in this matchup. Opponent is elite defense (#2) at slow pace (#24). 8/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; Defense, Pace dissent. Projection model targets 14.8 pts (4.3 pts above line; 62% blended confidence [T2]). Risk: high variance (σ=7.1) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Derrick White</t>
+          <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -9538,36 +9538,36 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.577</v>
+        <v>0.555</v>
       </c>
       <c r="F17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>15.3</v>
+        <v>18.6</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J17" t="n">
-        <v>1.917</v>
+        <v>2.85</v>
       </c>
       <c r="K17" t="n">
-        <v>1.82</v>
+        <v>1.4</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 3.4 pts (L5 vs L30) — supports the UNDER. Opponent is below-average defense (#20) at fast pace (#5). 7/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Defense, Pace, FG Trend dissent. Projection model targets 15.3 pts (2.2 pts below line; 57% blended confidence [T2]). Risk: high variance (σ=7.8) makes the outcome difficult to call with confidence.</t>
+          <t>Alexander-Walker's L30 of 20.6 pts sits 3.1 above the 17.5 line — supports the OVER. H2H avg 7.2 pts below season L30; FG% +6.3% trending (L10 vs L30). Opponent is elite defense (#2) at slow pace (#24). 6/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; Defense, H2H, Pace dissent. Projection model targets 18.6 pts (1.1 pts above line; 55% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Jalen Johnson</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -9586,36 +9586,36 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.547</v>
+        <v>0.539</v>
       </c>
       <c r="F18" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>28.7</v>
+        <v>20</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>1.926</v>
+        <v>2.9</v>
       </c>
       <c r="K18" t="n">
-        <v>1.82</v>
+        <v>1.385</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 5.2 pts (L5 vs L30) — supports the OVER. H2H avg 3.4 pts above season L30. Opponent is below-average defense (#20) at fast pace (#5). 7/10 signals agree — HR L10, Trend, Context, Defense support the OVER; Volume, HR L30, Min Trend dissent. Projection model targets 28.7 pts (1.2 pts above line; 54% blended confidence [T3]). Risk: high variance (σ=9.5) makes the outcome difficult to call with confidence.</t>
+          <t>Johnson averages 18.7 pts in 6 meetings (-2.8 vs line) — marginally supports the UNDER. H2H avg 3.3 pts below season L30; TS% shifts -7.9% in this matchup. Opponent is elite defense (#2) at slow pace (#24). Mixed signals: 4/10 agree (Context, Defense, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 20.0 pts (1.5 pts below line; 53% blended confidence [T3]). Risk: L3 has surged to 27.3 after a 29-pt outing (5.3 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Onyeka Okongwu</t>
+          <t>CJ McCollum</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -9625,7 +9625,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -9634,36 +9634,36 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.589</v>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>13.7</v>
+        <v>14.1</v>
       </c>
       <c r="I19" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8</v>
+        <v>2.85</v>
       </c>
       <c r="K19" t="n">
-        <v>1.935</v>
+        <v>1.4</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Okongwu averages 16.3 pts in 6 meetings (+4.8 vs line) — marginally supports the OVER. H2H avg 2.2 pts above season L30; TS% shifts +5.9% in this matchup. Opponent is elite defense (#2) at slow pace (#24). Mixed signals: 4/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 13.7 pts (2.2 pts above line; 55% blended confidence [T3]).</t>
+          <t>McCollum averages 14.3 pts in 7 meetings (-3.2 vs line) — marginally supports the UNDER. H2H avg 4.9 pts below season L30; TS% shifts -10.6% in this matchup. Opponent is elite defense (#2) at slow pace (#24). Mixed signals: 3/10 agree (Defense, H2H, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 14.1 pts (3.4 pts below line; 58% blended confidence [T3]). Risk: L3 has surged to 23.3 after a 17-pt outing (4.1 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Zaccharie Risacher</t>
+          <t>Jonathan Kuminga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -9682,36 +9682,36 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.554</v>
+        <v>0.586</v>
       </c>
       <c r="F20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J20" t="n">
-        <v>1.87</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>1.87</v>
+        <v>1.364</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Risacher averages 9.7 pts in 3 meetings (+4.2 vs line) — supports the OVER. TS% shifts -12.0% in this matchup; FG% +6.8% trending (L10 vs L30). Opponent is elite defense (#2) at slow pace (#24). 7/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; Defense, Pace, Min Trend dissent. Projection model targets 6.2 pts (0.7 pts above line; 55% blended confidence [T3]). Risk: minutes trending down (18.7 L10 vs 22.0 L30) — role reduction would suppress counting stats.</t>
+          <t>Kuminga's L30 of 12.0 pts sits 4.5 above the 7.5 line — marginally supports the UNDER. Opponent is elite defense (#2) at slow pace (#24). Mixed signals: 5/10 agree (Trend, Defense, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 4.3 pts (3.2 pts below line; 58% blended confidence [T3]). Risk: high variance (σ=8.6) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sam Hauser</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9730,36 +9730,36 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.524</v>
+        <v>0.547</v>
       </c>
       <c r="F21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>9.4</v>
+        <v>28.7</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J21" t="n">
-        <v>1.855</v>
+        <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>1.87</v>
+        <v>1.364</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Hauser averages 11.3 pts in 6 meetings (+2.8 vs line) — supports the OVER. H2H avg 2.1 pts above season L30; FG% -5.1% trending (L10 vs L30). Opponent is weak defense (#24) at fast pace (#5). 6/10 signals agree — Volume, HR L30, Context, Defense support the OVER; HR L10, Trend, FG Trend dissent. Projection model targets 9.4 pts (0.9 pts above line; 52% blended confidence [T3]).</t>
+          <t>Recent scoring trending up 5.2 pts (L5 vs L30) — supports the OVER. H2H avg 3.4 pts above season L30. Opponent is below-average defense (#20) at fast pace (#5). 7/10 signals agree — HR L10, Trend, Context, Defense support the OVER; Volume, HR L30, Min Trend dissent. Projection model targets 28.7 pts (1.2 pts above line; 54% blended confidence [T3]). Risk: high variance (σ=9.5) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Dyson Daniels</t>
+          <t>Payton Pritchard</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9774,40 +9774,40 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.625</v>
+        <v>0.574</v>
       </c>
       <c r="F22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>14.8</v>
+        <v>21.4</v>
       </c>
       <c r="I22" t="n">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="J22" t="n">
-        <v>1.87</v>
+        <v>2.75</v>
       </c>
       <c r="K22" t="n">
-        <v>1.855</v>
+        <v>1.417</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Daniels averages 16.0 pts in 5 meetings (+5.5 vs line) — supports the OVER. H2H avg 4.4 pts above season L30; TS% shifts +7.2% in this matchup. Opponent is elite defense (#2) at slow pace (#24). 8/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; Defense, Pace dissent. Projection model targets 14.8 pts (4.3 pts above line; 62% blended confidence [T2]). Risk: high variance (σ=7.1) makes the outcome difficult to call with confidence.</t>
+          <t>Recent scoring trending up 3.6 pts (L5 vs L30) — supports the OVER. TS% shifts +8.2% in this matchup. Opponent is below-average defense (#20) at fast pace (#5). 7/10 signals agree — HR L30, Trend, Context, Defense support the OVER; Volume, HR L10, H2H dissent. Projection model targets 21.4 pts (2.9 pts above line; 57% blended confidence [T3]). Risk: high variance (σ=8.9) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nickeil Alexander-Walker</t>
+          <t>Derrick White</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -9826,36 +9826,36 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.555</v>
+        <v>0.577</v>
       </c>
       <c r="F23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>18.6</v>
+        <v>15.3</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J23" t="n">
-        <v>1.87</v>
+        <v>2.9</v>
       </c>
       <c r="K23" t="n">
-        <v>1.87</v>
+        <v>1.385</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Alexander-Walker's L30 of 20.6 pts sits 3.1 above the 17.5 line — supports the OVER. H2H avg 7.2 pts below season L30; FG% +6.3% trending (L10 vs L30). Opponent is elite defense (#2) at slow pace (#24). 6/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; Defense, H2H, Pace dissent. Projection model targets 18.6 pts (1.1 pts above line; 55% blended confidence [T2]).</t>
+          <t>Recent scoring trending down 3.4 pts (L5 vs L30) — supports the UNDER. Opponent is below-average defense (#20) at fast pace (#5). 7/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Defense, Pace, FG Trend dissent. Projection model targets 15.3 pts (2.2 pts below line; 57% blended confidence [T2]). Risk: high variance (σ=7.8) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Sam Hauser</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -9874,36 +9874,36 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.539</v>
+        <v>0.524</v>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>20</v>
+        <v>9.4</v>
       </c>
       <c r="I24" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
-        <v>1.826</v>
+        <v>2.8</v>
       </c>
       <c r="K24" t="n">
-        <v>1.909</v>
+        <v>1.408</v>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Johnson averages 18.7 pts in 6 meetings (-2.8 vs line) — marginally supports the UNDER. H2H avg 3.3 pts below season L30; TS% shifts -7.9% in this matchup. Opponent is elite defense (#2) at slow pace (#24). Mixed signals: 4/10 agree (Context, Defense, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 20.0 pts (1.5 pts below line; 53% blended confidence [T3]). Risk: L3 has surged to 27.3 after a 29-pt outing (5.3 above L30) — momentum could push over the under line.</t>
+          <t>Hauser averages 11.3 pts in 6 meetings (+2.8 vs line) — supports the OVER. H2H avg 2.1 pts above season L30; FG% -5.1% trending (L10 vs L30). Opponent is weak defense (#24) at fast pace (#5). 6/10 signals agree — Volume, HR L30, Context, Defense support the OVER; HR L10, Trend, FG Trend dissent. Projection model targets 9.4 pts (0.9 pts above line; 52% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CJ McCollum</t>
+          <t>Jayson Tatum</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -9922,36 +9922,36 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.589</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>14.1</v>
+        <v>21.6</v>
       </c>
       <c r="I25" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="K25" t="n">
-        <v>1.935</v>
+        <v>1.408</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>McCollum averages 14.3 pts in 7 meetings (-3.2 vs line) — marginally supports the UNDER. H2H avg 4.9 pts below season L30; TS% shifts -10.6% in this matchup. Opponent is elite defense (#2) at slow pace (#24). Mixed signals: 3/10 agree (Defense, H2H, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 14.1 pts (3.4 pts below line; 58% blended confidence [T3]). Risk: L3 has surged to 23.3 after a 17-pt outing (4.1 above L30) — momentum could push over the under line.</t>
+          <t>Tatum's L30 of 24.7 pts sits 4.2 above the 20.5 line — supports the OVER. TS% shifts -6.0% in this matchup; Minutes down 3.2 recently (L10=31.4 vs L30=34.6). Opponent is weak defense (#24) at fast pace (#5). 6/10 signals agree — Volume, HR L30, Context, Defense support the OVER; HR L10, Trend, FG Trend dissent. Projection model targets 21.6 pts (1.1 pts above line; 56% blended confidence [T3]). Risk: minutes trending down (31.4 L10 vs 34.6 L30) — role reduction would suppress counting stats.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jonathan Kuminga</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -9970,29 +9970,29 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.586</v>
+        <v>0.519</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>4.3</v>
+        <v>8.1</v>
       </c>
       <c r="I26" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="J26" t="n">
-        <v>1.82</v>
+        <v>2.8</v>
       </c>
       <c r="K26" t="n">
-        <v>1.917</v>
+        <v>1.408</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Kuminga's L30 of 12.0 pts sits 4.5 above the 7.5 line — marginally supports the UNDER. Opponent is elite defense (#2) at slow pace (#24). Mixed signals: 5/10 agree (Trend, Defense, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 4.3 pts (3.2 pts below line; 58% blended confidence [T3]). Risk: high variance (σ=8.6) makes the outcome difficult to call with confidence.</t>
+          <t>Queta averages 6.2 pts in 5 meetings (-2.3 vs line) — marginally supports the UNDER. H2H avg 3.3 pts below season L30; TS% shifts +6.7% in this matchup. Opponent is below-average defense (#17) at fast pace (#5). Mixed signals: 3/10 agree (HR L30, HR L10, H2H); counter-signals: Volume, Trend, Context. Projection model targets 8.1 pts (0.4 pts below line; 51% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -10033,10 +10033,10 @@
         <v>2.3</v>
       </c>
       <c r="J27" t="n">
-        <v>1.833</v>
+        <v>1.8</v>
       </c>
       <c r="K27" t="n">
-        <v>1.885</v>
+        <v>1.952</v>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
@@ -10081,10 +10081,10 @@
         <v>6.6</v>
       </c>
       <c r="J28" t="n">
-        <v>1.893</v>
+        <v>1.606</v>
       </c>
       <c r="K28" t="n">
-        <v>1.833</v>
+        <v>2.18</v>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
@@ -10129,10 +10129,10 @@
         <v>6.8</v>
       </c>
       <c r="J29" t="n">
+        <v>1.971</v>
+      </c>
+      <c r="K29" t="n">
         <v>1.746</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2</v>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
@@ -10177,10 +10177,10 @@
         <v>9.699999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>1.847</v>
+        <v>1.645</v>
       </c>
       <c r="K30" t="n">
-        <v>1.885</v>
+        <v>2.12</v>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
@@ -10225,10 +10225,10 @@
         <v>3.1</v>
       </c>
       <c r="J31" t="n">
-        <v>1.787</v>
+        <v>2.02</v>
       </c>
       <c r="K31" t="n">
-        <v>1.952</v>
+        <v>1.719</v>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
@@ -10273,10 +10273,10 @@
         <v>3.3</v>
       </c>
       <c r="J32" t="n">
-        <v>1.8</v>
+        <v>1.787</v>
       </c>
       <c r="K32" t="n">
-        <v>1.943</v>
+        <v>1.935</v>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
@@ -10321,10 +10321,10 @@
         <v>0.6</v>
       </c>
       <c r="J33" t="n">
-        <v>1.87</v>
+        <v>1.645</v>
       </c>
       <c r="K33" t="n">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Luke Kornet</t>
+          <t>Collin Sexton</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -10345,7 +10345,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -10354,7 +10354,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.592</v>
       </c>
       <c r="F34" t="n">
         <v>6</v>
@@ -10363,27 +10363,27 @@
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>3.3</v>
+        <v>19.6</v>
       </c>
       <c r="I34" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="J34" t="n">
-        <v>1.826</v>
+        <v>2.05</v>
       </c>
       <c r="K34" t="n">
-        <v>1.909</v>
+        <v>1.699</v>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>Low scoring variance (σ=3.7) — highly predictable output near line — supports the UNDER. TS% shifts -3.9% in this matchup; FG% -9.6% trending (L10 vs L30). Opponent is weak defense (#26) at fast pace (#2). 6/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Defense, H2H, Pace dissent. Projection model targets 3.3 pts (2.2 pts below line; 55% blended confidence [T2]).</t>
+          <t>Recent scoring trending up 4.7 pts (L5 vs L30) — supports the OVER. H2H avg 4.7 pts above season L30; TS% shifts +7.6% in this matchup. Opponent is strong defense (#8) at above-average pace (#9). 6/10 signals agree — HR L10, Trend, H2H, Pace support the OVER; Volume, HR L30, Context dissent. Projection model targets 19.6 pts (3.1 pts above line; 59% blended confidence [T2]). Risk: only 40% hit rate over L30 suggests the line may be set fairly.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Collin Sexton</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -10393,45 +10393,45 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.592</v>
+        <v>0.519</v>
       </c>
       <c r="F35" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>19.6</v>
+        <v>14.6</v>
       </c>
       <c r="I35" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="K35" t="n">
-        <v>1.87</v>
+        <v>1.719</v>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 4.7 pts (L5 vs L30) — supports the OVER. H2H avg 4.7 pts above season L30; TS% shifts +7.6% in this matchup. Opponent is strong defense (#8) at above-average pace (#9). 6/10 signals agree — HR L10, Trend, H2H, Pace support the OVER; Volume, HR L30, Context dissent. Projection model targets 19.6 pts (3.1 pts above line; 59% blended confidence [T2]). Risk: only 40% hit rate over L30 suggests the line may be set fairly.</t>
+          <t>Castle's L30 average of 15.8 pts vs the 15.5 line — marginally supports the UNDER. H2H avg 2.1 pts below season L30; TS% shifts -4.6% in this matchup. Opponent is below-average defense (#18) at fast pace (#2). Mixed signals: 3/10 agree (Context, H2H, FG Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 14.6 pts (0.9 pts below line; 51% blended confidence [T3]). Risk: high variance (σ=8.1) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Isaac Okoro</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -10450,7 +10450,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.519</v>
+        <v>0.542</v>
       </c>
       <c r="F36" t="n">
         <v>3</v>
@@ -10459,10 +10459,10 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>14.6</v>
+        <v>7</v>
       </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>1.787</v>
@@ -10472,14 +10472,14 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Castle's L30 average of 15.8 pts vs the 15.5 line — marginally supports the UNDER. H2H avg 2.1 pts below season L30; TS% shifts -4.6% in this matchup. Opponent is below-average defense (#18) at fast pace (#2). Mixed signals: 3/10 agree (Context, H2H, FG Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 14.6 pts (0.9 pts below line; 51% blended confidence [T3]). Risk: high variance (σ=8.1) makes the outcome difficult to call with confidence.</t>
+          <t>Okoro averages 5.7 pts in 3 meetings (-2.8 vs line) — marginally supports the UNDER. H2H avg 4.1 pts below season L30; TS% shifts -11.9% in this matchup. Opponent is strong defense (#8) at above-average pace (#9). Mixed signals: 3/10 agree (Defense, H2H, FG Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 7.0 pts (1.5 pts below line; 54% blended confidence [T3]). Risk: 63% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Isaac Okoro</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -10489,7 +10489,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -10498,36 +10498,36 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.542</v>
+        <v>0.602</v>
       </c>
       <c r="F37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>7</v>
+        <v>30.2</v>
       </c>
       <c r="I37" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J37" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="K37" t="n">
-        <v>1.758</v>
+        <v>1.599</v>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>Okoro averages 5.7 pts in 3 meetings (-2.8 vs line) — marginally supports the UNDER. H2H avg 4.1 pts below season L30; TS% shifts -11.9% in this matchup. Opponent is strong defense (#8) at above-average pace (#9). Mixed signals: 3/10 agree (Defense, H2H, FG Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 7.0 pts (1.5 pts below line; 54% blended confidence [T3]). Risk: 63% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
+          <t>Wembanyama's L30 of 23.6 pts sits 2.9 below the 26.5 line — marginally supports the OVER. Opponent is weak defense (#28) at fast pace (#2). Mixed signals: 4/10 agree (Trend, Defense, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 30.2 pts (3.7 pts above line; 60% blended confidence [T3]). Risk: high variance (σ=7.2) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Keldon Johnson</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -10542,40 +10542,40 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.602</v>
+        <v>0.614</v>
       </c>
       <c r="F38" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>30.2</v>
+        <v>15.7</v>
       </c>
       <c r="I38" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="J38" t="n">
-        <v>1.877</v>
+        <v>1.787</v>
       </c>
       <c r="K38" t="n">
-        <v>1.855</v>
+        <v>1.935</v>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Wembanyama's L30 of 23.6 pts sits 2.9 below the 26.5 line — marginally supports the OVER. Opponent is weak defense (#28) at fast pace (#2). Mixed signals: 4/10 agree (Trend, Defense, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 30.2 pts (3.7 pts above line; 60% blended confidence [T3]). Risk: high variance (σ=7.2) makes the outcome difficult to call with confidence.</t>
+          <t>Johnson averages 16.3 pts in 3 meetings (+3.8 vs line) — supports the OVER. H2H avg 3.6 pts above season L30; FG% +3.2% trending (L10 vs L30). Opponent is weak defense (#28) at fast pace (#2). 9/10 signals agree — Volume, HR L10, Trend, Context support the OVER; HR L30 dissents. Projection model targets 15.7 pts (3.2 pts above line; 61% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Keldon Johnson</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -10585,45 +10585,45 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.614</v>
+        <v>0.524</v>
       </c>
       <c r="F39" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>15.7</v>
+        <v>12.9</v>
       </c>
       <c r="I39" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
-        <v>1.893</v>
+        <v>1.847</v>
       </c>
       <c r="K39" t="n">
-        <v>1.833</v>
+        <v>1.87</v>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Johnson averages 16.3 pts in 3 meetings (+3.8 vs line) — supports the OVER. H2H avg 3.6 pts above season L30; FG% +3.2% trending (L10 vs L30). Opponent is weak defense (#28) at fast pace (#2). 9/10 signals agree — Volume, HR L10, Trend, Context support the OVER; HR L30 dissents. Projection model targets 15.7 pts (3.2 pts above line; 61% blended confidence [T2]).</t>
+          <t>Recent scoring trending up 2.2 pts (L5 vs L30) — marginally supports the UNDER. Opponent is below-average defense (#18) at fast pace (#2). Mixed signals: 3/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 12.9 pts (0.6 pts below line; 52% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Matas Buzelis</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -10642,36 +10642,36 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.524</v>
+        <v>0.521</v>
       </c>
       <c r="F40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>12.9</v>
+        <v>16.8</v>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
-        <v>1.909</v>
+        <v>1.962</v>
       </c>
       <c r="K40" t="n">
-        <v>1.826</v>
+        <v>1.758</v>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 2.2 pts (L5 vs L30) — marginally supports the UNDER. Opponent is below-average defense (#18) at fast pace (#2). Mixed signals: 3/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 12.9 pts (0.6 pts below line; 52% blended confidence [T3]).</t>
+          <t>Buzelis averages 8.7 pts in 3 meetings (-8.8 vs line) — marginally supports the UNDER. H2H avg 9.8 pts below season L30; TS% shifts +4.3% in this matchup. Opponent is strong defense (#8) at above-average pace (#9). Mixed signals: 2/10 agree (Defense, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 16.8 pts (0.7 pts below line; 52% blended confidence [T3]). Risk: high variance (σ=8.3) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Matas Buzelis</t>
+          <t>Luke Kornet</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -10681,38 +10681,38 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T3_LEAN</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.539</v>
+        <v>0.541</v>
       </c>
       <c r="F41" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>16.5</v>
+        <v>3.4</v>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="J41" t="n">
-        <v>1.885</v>
+        <v>1.833</v>
       </c>
       <c r="K41" t="n">
-        <v>1.833</v>
+        <v>1.909</v>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>Buzelis averages 8.7 pts in 3 meetings (-9.8 vs line) — marginally supports the UNDER. H2H avg 9.8 pts below season L30; TS% shifts +4.3% in this matchup. Opponent is strong defense (#8) at above-average pace (#9). Mixed signals: 4/10 agree (HR L30, Context, Defense); counter-signals: Volume, HR L10, Trend. Projection model targets 16.5 pts (2.0 pts below line; 53% blended confidence [T3]). Risk: high variance (σ=8.3) makes the outcome difficult to call with confidence.</t>
+          <t>[Low conviction — lean only] Kornet averages 5.5 pts in 4 meetings (+2.0 vs line) — supports the lean OVER. TS% shifts -3.9% in this matchup; FG% -9.6% trending (L10 vs L30). Opponent is weak defense (#26) at fast pace (#2). 8/10 signals agree — Volume, HR L30, HR L10, Context support the OVER; Trend, FG Trend dissent. Projection model targets 3.4 pts (0.1 pts below line; 54% blended confidence [T3_LEAN]).</t>
         </is>
       </c>
     </row>
@@ -10738,10 +10738,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.579</v>
+        <v>0.608</v>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -10750,17 +10750,17 @@
         <v>8</v>
       </c>
       <c r="I42" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="J42" t="n">
-        <v>1.952</v>
+        <v>1.87</v>
       </c>
       <c r="K42" t="n">
-        <v>1.775</v>
+        <v>1.87</v>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Gillespie averages 8.0 pts in 3 meetings (-3.5 vs line) — marginally supports the UNDER. H2H avg 4.7 pts below season L30; FG% -5.6% trending (L10 vs L30). Opponent is below-average defense (#22) at above-average pace (#6). Mixed signals: 3/10 agree (H2H, FG Trend, Min Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 8.0 pts (3.5 pts below line; 57% blended confidence [T3]). Risk: high variance (σ=8.1) makes the outcome difficult to call with confidence.</t>
+          <t>Gillespie averages 8.0 pts in 3 meetings (-4.5 vs line) — supports the UNDER. H2H avg 4.7 pts below season L30; FG% -5.6% trending (L10 vs L30). Opponent is below-average defense (#22) at above-average pace (#6). 6/10 signals agree — HR L30, HR L10, Context, H2H support the UNDER; Volume, Trend, Defense dissent. Projection model targets 8.0 pts (4.5 pts below line; 60% blended confidence [T3]). Risk: high variance (σ=8.1) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
@@ -10801,10 +10801,10 @@
         <v>2.3</v>
       </c>
       <c r="J43" t="n">
-        <v>1.943</v>
+        <v>1.952</v>
       </c>
       <c r="K43" t="n">
-        <v>1.787</v>
+        <v>1.8</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.573</v>
+        <v>0.603</v>
       </c>
       <c r="F44" t="n">
         <v>4</v>
@@ -10846,17 +10846,17 @@
         <v>5.7</v>
       </c>
       <c r="I44" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="J44" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="K44" t="n">
-        <v>1.87</v>
+        <v>1.769</v>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Low scoring variance (σ=3.1) — highly predictable output near line — marginally supports the UNDER. Opponent is below-average defense (#22) at above-average pace (#6). Mixed signals: 4/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, H2H. Projection model targets 5.7 pts (2.8 pts below line; 57% blended confidence [T3]).</t>
+          <t>Low scoring variance (σ=3.1) — highly predictable output near line — marginally supports the UNDER. Opponent is below-average defense (#22) at above-average pace (#6). Mixed signals: 4/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, H2H. Projection model targets 5.7 pts (3.8 pts below line; 60% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -10897,10 +10897,10 @@
         <v>9.9</v>
       </c>
       <c r="J45" t="n">
-        <v>1.847</v>
+        <v>1.87</v>
       </c>
       <c r="K45" t="n">
-        <v>1.877</v>
+        <v>1.87</v>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
@@ -10930,10 +10930,10 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.546</v>
+        <v>0.581</v>
       </c>
       <c r="F46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -10942,17 +10942,17 @@
         <v>18.3</v>
       </c>
       <c r="I46" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J46" t="n">
+        <v>1.769</v>
+      </c>
+      <c r="K46" t="n">
         <v>1.952</v>
       </c>
-      <c r="K46" t="n">
-        <v>1.787</v>
-      </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Allen averages 14.4 pts in 5 meetings (-2.1 vs line) — marginally supports the OVER. H2H avg 3.1 pts below season L30; TS% shifts +8.4% in this matchup. Opponent is below-average defense (#22) at above-average pace (#6). Mixed signals: 4/10 agree (Volume, Context, Defense); counter-signals: HR L30, HR L10, Trend. Projection model targets 18.3 pts (1.8 pts above line; 54% blended confidence [T3]).</t>
+          <t>Allen's L30 of 17.5 pts sits 2.0 above the 15.5 line — marginally supports the OVER. H2H avg 3.1 pts below season L30; TS% shifts +8.4% in this matchup. Opponent is below-average defense (#22) at above-average pace (#6). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, H2H. Projection model targets 18.3 pts (2.8 pts above line; 58% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -10993,10 +10993,10 @@
         <v>5.1</v>
       </c>
       <c r="J47" t="n">
-        <v>1.769</v>
+        <v>1.8</v>
       </c>
       <c r="K47" t="n">
-        <v>2</v>
+        <v>1.952</v>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
@@ -11041,10 +11041,10 @@
         <v>5.4</v>
       </c>
       <c r="J48" t="n">
-        <v>1.806</v>
+        <v>1.8</v>
       </c>
       <c r="K48" t="n">
-        <v>1.926</v>
+        <v>1.952</v>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
@@ -11089,10 +11089,10 @@
         <v>2.1</v>
       </c>
       <c r="J49" t="n">
-        <v>1.826</v>
+        <v>1.952</v>
       </c>
       <c r="K49" t="n">
-        <v>1.909</v>
+        <v>1.8</v>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         <v>5.7</v>
       </c>
       <c r="J50" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="K50" t="n">
         <v>1.926</v>
-      </c>
-      <c r="K50" t="n">
-        <v>1.82</v>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
@@ -11170,10 +11170,10 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.657</v>
+        <v>0.591</v>
       </c>
       <c r="F51" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -11182,17 +11182,17 @@
         <v>26.4</v>
       </c>
       <c r="I51" t="n">
-        <v>5.9</v>
+        <v>3.9</v>
       </c>
       <c r="J51" t="n">
-        <v>1.775</v>
+        <v>1.901</v>
       </c>
       <c r="K51" t="n">
-        <v>1.962</v>
+        <v>1.833</v>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Green averages 29.0 pts in 4 meetings (+8.5 vs line) — supports the OVER. H2H avg 12.0 pts above season L30; TS% shifts +11.3% in this matchup. Opponent is below-average defense (#22) at above-average pace (#6). 7/10 signals agree — HR L10, Trend, Defense, H2H support the OVER; Volume, HR L30, Context dissent. Projection model targets 26.4 pts (5.9 pts above line; 65% blended confidence [T3]). Risk: high variance (σ=8.2) makes the outcome difficult to call with confidence.</t>
+          <t>Green averages 29.0 pts in 4 meetings (+6.5 vs line) — supports the OVER. H2H avg 12.0 pts above season L30; TS% shifts +11.3% in this matchup. Opponent is below-average defense (#22) at above-average pace (#6). 6/10 signals agree — Trend, Defense, H2H, Pace support the OVER; Volume, HR L30, HR L10 dissent. Projection model targets 26.4 pts (3.9 pts above line; 59% blended confidence [T3]). Risk: high variance (σ=8.2) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
@@ -11218,29 +11218,29 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.521</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="I52" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J52" t="n">
-        <v>1.877</v>
+        <v>1.833</v>
       </c>
       <c r="K52" t="n">
-        <v>1.855</v>
+        <v>1.901</v>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 3.8 pts (L5 vs L30) — marginally supports the UNDER. H2H avg 3.6 pts below season L30; TS% shifts -6.6% in this matchup. Opponent is below-average defense (#22) at above-average pace (#6). Mixed signals: 3/10 agree (Trend, Context, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 24.2 pts (1.3 pts below line; 52% blended confidence [T3]). Risk: high variance (σ=8.8) makes the outcome difficult to call with confidence.</t>
+          <t>Booker averages 22.0 pts in 6 meetings (-4.5 vs line) — marginally supports the UNDER. H2H avg 3.6 pts below season L30; TS% shifts -6.6% in this matchup. Opponent is below-average defense (#22) at above-average pace (#6). Mixed signals: 4/10 agree (Volume, Trend, Context); counter-signals: HR L30, HR L10, Defense. Projection model targets 24.1 pts (2.4 pts below line; 55% blended confidence [T3]). Risk: high variance (σ=8.8) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
@@ -11281,10 +11281,10 @@
         <v>3</v>
       </c>
       <c r="J53" t="n">
-        <v>1.847</v>
+        <v>1.833</v>
       </c>
       <c r="K53" t="n">
-        <v>1.877</v>
+        <v>1.909</v>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
@@ -11329,10 +11329,10 @@
         <v>4.7</v>
       </c>
       <c r="J54" t="n">
-        <v>2</v>
+        <v>1.952</v>
       </c>
       <c r="K54" t="n">
-        <v>1.769</v>
+        <v>1.8</v>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
@@ -11377,10 +11377,10 @@
         <v>2</v>
       </c>
       <c r="J55" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="K55" t="n">
-        <v>1.787</v>
+        <v>1.87</v>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
@@ -11425,10 +11425,10 @@
         <v>4.5</v>
       </c>
       <c r="J56" t="n">
+        <v>1.909</v>
+      </c>
+      <c r="K56" t="n">
         <v>1.833</v>
-      </c>
-      <c r="K56" t="n">
-        <v>1.926</v>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
@@ -11473,10 +11473,10 @@
         <v>6.2</v>
       </c>
       <c r="J57" t="n">
-        <v>1.917</v>
+        <v>1.952</v>
       </c>
       <c r="K57" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
@@ -11521,10 +11521,10 @@
         <v>4</v>
       </c>
       <c r="J58" t="n">
-        <v>1.813</v>
+        <v>1.952</v>
       </c>
       <c r="K58" t="n">
-        <v>1.952</v>
+        <v>1.8</v>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
@@ -11569,10 +11569,10 @@
         <v>0.1</v>
       </c>
       <c r="J59" t="n">
-        <v>1.952</v>
+        <v>1.909</v>
       </c>
       <c r="K59" t="n">
-        <v>1.813</v>
+        <v>1.833</v>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
@@ -11617,10 +11617,10 @@
         <v>6.5</v>
       </c>
       <c r="J60" t="n">
-        <v>1.847</v>
+        <v>1.952</v>
       </c>
       <c r="K60" t="n">
-        <v>1.909</v>
+        <v>1.8</v>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
@@ -11665,10 +11665,10 @@
         <v>0.1</v>
       </c>
       <c r="J61" t="n">
-        <v>1.952</v>
+        <v>1.87</v>
       </c>
       <c r="K61" t="n">
-        <v>1.813</v>
+        <v>1.87</v>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
@@ -11713,10 +11713,10 @@
         <v>6.1</v>
       </c>
       <c r="J62" t="n">
-        <v>1.82</v>
+        <v>1.833</v>
       </c>
       <c r="K62" t="n">
-        <v>1.943</v>
+        <v>1.901</v>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>1.952</v>
       </c>
       <c r="K63" t="n">
-        <v>1.813</v>
+        <v>1.8</v>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
@@ -11809,7 +11809,7 @@
         <v>0.1</v>
       </c>
       <c r="J64" t="n">
-        <v>1.813</v>
+        <v>1.769</v>
       </c>
       <c r="K64" t="n">
         <v>1.952</v>
@@ -11857,10 +11857,10 @@
         <v>1.3</v>
       </c>
       <c r="J65" t="n">
-        <v>1.8</v>
+        <v>1.833</v>
       </c>
       <c r="K65" t="n">
-        <v>1.971</v>
+        <v>1.909</v>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
@@ -11905,10 +11905,10 @@
         <v>4.7</v>
       </c>
       <c r="J66" t="n">
-        <v>1.943</v>
+        <v>1.87</v>
       </c>
       <c r="K66" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
@@ -11953,10 +11953,10 @@
         <v>0.1</v>
       </c>
       <c r="J67" t="n">
-        <v>1.917</v>
+        <v>1.813</v>
       </c>
       <c r="K67" t="n">
-        <v>1.84</v>
+        <v>1.952</v>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
@@ -12049,10 +12049,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="J69" t="n">
-        <v>1.806</v>
+        <v>1.952</v>
       </c>
       <c r="K69" t="n">
-        <v>1.935</v>
+        <v>1.8</v>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
@@ -12097,10 +12097,10 @@
         <v>1.8</v>
       </c>
       <c r="J70" t="n">
-        <v>1.82</v>
+        <v>1.833</v>
       </c>
       <c r="K70" t="n">
-        <v>1.962</v>
+        <v>1.901</v>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
@@ -12145,10 +12145,10 @@
         <v>0.9</v>
       </c>
       <c r="J71" t="n">
-        <v>1.806</v>
+        <v>1.952</v>
       </c>
       <c r="K71" t="n">
-        <v>1.971</v>
+        <v>1.8</v>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
@@ -12193,10 +12193,10 @@
         <v>2.8</v>
       </c>
       <c r="J72" t="n">
-        <v>1.952</v>
+        <v>1.87</v>
       </c>
       <c r="K72" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
@@ -12241,10 +12241,10 @@
         <v>11.4</v>
       </c>
       <c r="J73" t="n">
-        <v>1.847</v>
+        <v>1.8</v>
       </c>
       <c r="K73" t="n">
-        <v>1.926</v>
+        <v>1.952</v>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
@@ -12274,10 +12274,10 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.58</v>
+        <v>0.591</v>
       </c>
       <c r="F74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -12286,17 +12286,17 @@
         <v>5.3</v>
       </c>
       <c r="I74" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="J74" t="n">
-        <v>1.826</v>
+        <v>1.943</v>
       </c>
       <c r="K74" t="n">
-        <v>1.909</v>
+        <v>1.833</v>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Low scoring variance (σ=3.0) — highly predictable output near line — marginally supports the UNDER. FG% +8.4% trending (L10 vs L30). Opponent is below-average defense (#22) at above-average pace (#7). Mixed signals: 2/10 agree (Volume, Context); counter-signals: HR L30, HR L10, Trend. Projection model targets 5.3 pts (2.2 pts below line; 57% blended confidence [T3]).</t>
+          <t>Low scoring variance (σ=3.0) — highly predictable output near line — marginally supports the UNDER. FG% +8.4% trending (L10 vs L30). Opponent is below-average defense (#22) at above-average pace (#7). Mixed signals: 3/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 5.3 pts (3.2 pts below line; 59% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -12322,10 +12322,10 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.536</v>
+        <v>0.552</v>
       </c>
       <c r="F75" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -12334,17 +12334,17 @@
         <v>11.7</v>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J75" t="n">
-        <v>1.862</v>
+        <v>1.952</v>
       </c>
       <c r="K75" t="n">
-        <v>1.909</v>
+        <v>1.8</v>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Filipowski averages 7.3 pts in 3 meetings (-5.2 vs line) — marginally supports the UNDER. H2H avg 5.8 pts below season L30; FG% -7.1% trending (L10 vs L30). Opponent is below-average defense (#20) at above-average pace (#10). Mixed signals: 3/10 agree (Context, H2H, FG Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 11.7 pts (0.8 pts below line; 53% blended confidence [T3]). Risk: L3 has surged to 19.0 after a 16-pt outing (5.9 above L30) — momentum could push over the under line.</t>
+          <t>Filipowski averages 7.3 pts in 3 meetings (-6.2 vs line) — marginally supports the UNDER. H2H avg 5.8 pts below season L30; FG% -7.1% trending (L10 vs L30). Opponent is below-average defense (#20) at above-average pace (#10). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 11.7 pts (1.8 pts below line; 55% blended confidence [T3]). Risk: L3 has surged to 19.0 after a 16-pt outing (5.9 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
@@ -12385,10 +12385,10 @@
         <v>8.699999999999999</v>
       </c>
       <c r="J76" t="n">
-        <v>1.84</v>
+        <v>1.833</v>
       </c>
       <c r="K76" t="n">
-        <v>1.935</v>
+        <v>1.901</v>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.576</v>
+        <v>0.591</v>
       </c>
       <c r="F77" t="n">
         <v>4</v>
@@ -12430,17 +12430,17 @@
         <v>5.8</v>
       </c>
       <c r="I77" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="J77" t="n">
-        <v>2.02</v>
+        <v>1.714</v>
       </c>
       <c r="K77" t="n">
-        <v>1.769</v>
+        <v>2.05</v>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Ellis averages 4.5 pts in 6 meetings (-4.0 vs line) — marginally supports the UNDER. H2H avg 2.8 pts below season L30; FG% +8.6% trending (L10 vs L30). Opponent is weak defense (#30) at above-average pace (#7). Mixed signals: 4/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 5.8 pts (2.7 pts below line; 57% blended confidence [T3]).</t>
+          <t>Ellis averages 4.5 pts in 6 meetings (-5.0 vs line) — marginally supports the UNDER. H2H avg 2.8 pts below season L30; FG% +8.6% trending (L10 vs L30). Opponent is weak defense (#30) at above-average pace (#7). Mixed signals: 4/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 5.8 pts (3.7 pts below line; 59% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -12481,10 +12481,10 @@
         <v>0.5</v>
       </c>
       <c r="J78" t="n">
-        <v>1.99</v>
+        <v>1.833</v>
       </c>
       <c r="K78" t="n">
-        <v>1.794</v>
+        <v>1.901</v>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
@@ -12529,10 +12529,10 @@
         <v>2.6</v>
       </c>
       <c r="J79" t="n">
-        <v>1.885</v>
+        <v>1.87</v>
       </c>
       <c r="K79" t="n">
-        <v>1.885</v>
+        <v>1.87</v>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
@@ -12577,10 +12577,10 @@
         <v>1.9</v>
       </c>
       <c r="J80" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="K80" t="n">
-        <v>1.787</v>
+        <v>1.741</v>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
@@ -12625,10 +12625,10 @@
         <v>1.7</v>
       </c>
       <c r="J81" t="n">
-        <v>1.893</v>
+        <v>3.05</v>
       </c>
       <c r="K81" t="n">
-        <v>1.833</v>
+        <v>1.357</v>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
@@ -12673,10 +12673,10 @@
         <v>11.4</v>
       </c>
       <c r="J82" t="n">
-        <v>1.847</v>
+        <v>2.8</v>
       </c>
       <c r="K82" t="n">
-        <v>1.885</v>
+        <v>1.408</v>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
@@ -12721,10 +12721,10 @@
         <v>11</v>
       </c>
       <c r="J83" t="n">
-        <v>1.971</v>
+        <v>2.85</v>
       </c>
       <c r="K83" t="n">
-        <v>1.769</v>
+        <v>1.4</v>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
@@ -12769,10 +12769,10 @@
         <v>10.6</v>
       </c>
       <c r="J84" t="n">
-        <v>1.769</v>
+        <v>2.6</v>
       </c>
       <c r="K84" t="n">
-        <v>1.971</v>
+        <v>1.465</v>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
@@ -12817,10 +12817,10 @@
         <v>3.4</v>
       </c>
       <c r="J85" t="n">
-        <v>1.833</v>
+        <v>3.1</v>
       </c>
       <c r="K85" t="n">
-        <v>1.893</v>
+        <v>1.345</v>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
@@ -12865,10 +12865,10 @@
         <v>3</v>
       </c>
       <c r="J86" t="n">
-        <v>1.893</v>
+        <v>2.7</v>
       </c>
       <c r="K86" t="n">
-        <v>1.833</v>
+        <v>1.435</v>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
@@ -12913,10 +12913,10 @@
         <v>3.8</v>
       </c>
       <c r="J87" t="n">
-        <v>1.806</v>
+        <v>2.85</v>
       </c>
       <c r="K87" t="n">
-        <v>1.926</v>
+        <v>1.4</v>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
@@ -12961,10 +12961,10 @@
         <v>2.1</v>
       </c>
       <c r="J88" t="n">
-        <v>1.787</v>
+        <v>3.05</v>
       </c>
       <c r="K88" t="n">
-        <v>1.952</v>
+        <v>1.357</v>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
@@ -13009,10 +13009,10 @@
         <v>0.5</v>
       </c>
       <c r="J89" t="n">
-        <v>1.877</v>
+        <v>2.7</v>
       </c>
       <c r="K89" t="n">
-        <v>1.847</v>
+        <v>1.435</v>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
@@ -13038,11 +13038,11 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>T1_PREMIUM</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.68</v>
+        <v>0.648</v>
       </c>
       <c r="F90" t="n">
         <v>8</v>
@@ -13054,17 +13054,17 @@
         <v>9.1</v>
       </c>
       <c r="I90" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="J90" t="n">
-        <v>1.952</v>
+        <v>2.8</v>
       </c>
       <c r="K90" t="n">
-        <v>1.787</v>
+        <v>1.408</v>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>Reed's L30 of 8.6 pts sits 4.9 below the 13.5 line — supports the UNDER. FG% -5.2% trending (L10 vs L30). Opponent is strong defense (#8) at slow pace (#28). 8/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, H2H dissent. Projection model targets 9.1 pts (4.4 pts below line; 67% blended confidence [T1_PREMIUM]).</t>
+          <t>Reed's L30 of 8.6 pts sits 3.9 below the 12.5 line — supports the UNDER. FG% -5.2% trending (L10 vs L30). Opponent is strong defense (#8) at slow pace (#28). 8/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, H2H dissent. Projection model targets 9.1 pts (3.4 pts below line; 64% blended confidence [T1]).</t>
         </is>
       </c>
     </row>
@@ -13105,10 +13105,10 @@
         <v>0.4</v>
       </c>
       <c r="J91" t="n">
-        <v>1.847</v>
+        <v>2.9</v>
       </c>
       <c r="K91" t="n">
-        <v>1.885</v>
+        <v>1.385</v>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
@@ -13153,10 +13153,10 @@
         <v>0.9</v>
       </c>
       <c r="J92" t="n">
-        <v>1.943</v>
+        <v>1.935</v>
       </c>
       <c r="K92" t="n">
-        <v>1.8</v>
+        <v>1.787</v>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
@@ -13201,10 +13201,10 @@
         <v>1</v>
       </c>
       <c r="J93" t="n">
-        <v>1.769</v>
+        <v>1.746</v>
       </c>
       <c r="K93" t="n">
-        <v>1.971</v>
+        <v>2</v>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
@@ -13249,10 +13249,10 @@
         <v>1.2</v>
       </c>
       <c r="J94" t="n">
-        <v>1.893</v>
+        <v>1.847</v>
       </c>
       <c r="K94" t="n">
-        <v>1.833</v>
+        <v>1.877</v>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
@@ -13297,10 +13297,10 @@
         <v>13.5</v>
       </c>
       <c r="J95" t="n">
-        <v>1.826</v>
+        <v>2.15</v>
       </c>
       <c r="K95" t="n">
-        <v>1.909</v>
+        <v>1.637</v>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>2.7</v>
       </c>
       <c r="J96" t="n">
-        <v>1.952</v>
+        <v>1.943</v>
       </c>
       <c r="K96" t="n">
         <v>1.775</v>
@@ -13393,10 +13393,10 @@
         <v>5.5</v>
       </c>
       <c r="J97" t="n">
-        <v>1.885</v>
+        <v>1.637</v>
       </c>
       <c r="K97" t="n">
-        <v>1.833</v>
+        <v>2.15</v>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
@@ -13441,10 +13441,10 @@
         <v>4.5</v>
       </c>
       <c r="J98" t="n">
-        <v>1.943</v>
+        <v>1.637</v>
       </c>
       <c r="K98" t="n">
-        <v>1.787</v>
+        <v>2.14</v>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
@@ -13489,10 +13489,10 @@
         <v>2.4</v>
       </c>
       <c r="J99" t="n">
-        <v>1.775</v>
+        <v>2.02</v>
       </c>
       <c r="K99" t="n">
-        <v>1.962</v>
+        <v>1.719</v>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.659</v>
+        <v>0.617</v>
       </c>
       <c r="F100" t="n">
         <v>6</v>
@@ -13534,17 +13534,17 @@
         <v>8.5</v>
       </c>
       <c r="I100" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J100" t="n">
-        <v>1.893</v>
+        <v>1.806</v>
       </c>
       <c r="K100" t="n">
-        <v>1.833</v>
+        <v>1.909</v>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>Hachimura's L30 of 10.0 pts sits 3.5 below the 13.5 line — supports the UNDER. H2H avg 4.0 pts above season L30; TS% shifts +7.9% in this matchup. Opponent is weak defense (#30) at above-average pace (#11). 6/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Defense, H2H, Pace dissent. Projection model targets 8.5 pts (5.0 pts below line; 65% blended confidence [T3]).</t>
+          <t>Recent scoring trending down 3.8 pts (L5 vs L30) — supports the UNDER. H2H avg 4.0 pts above season L30; TS% shifts +7.9% in this matchup. Opponent is weak defense (#30) at above-average pace (#11). 6/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Defense, H2H, Pace dissent. Projection model targets 8.5 pts (4.0 pts below line; 61% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -13585,10 +13585,10 @@
         <v>3.8</v>
       </c>
       <c r="J101" t="n">
-        <v>1.909</v>
+        <v>1.893</v>
       </c>
       <c r="K101" t="n">
-        <v>1.82</v>
+        <v>1.826</v>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
@@ -13633,10 +13633,10 @@
         <v>6.5</v>
       </c>
       <c r="J102" t="n">
-        <v>1.833</v>
+        <v>1.826</v>
       </c>
       <c r="K102" t="n">
-        <v>1.909</v>
+        <v>1.885</v>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="3">
@@ -13767,7 +13767,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="5">
@@ -13827,7 +13827,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="8">
@@ -13953,7 +13953,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Payton Pritchard</t>
+          <t>Onyeka Okongwu</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -13967,13 +13967,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jayson Tatum</t>
+          <t>Zaccharie Risacher</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -13983,17 +13983,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>23.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Dyson Daniels</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -14013,7 +14013,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Derrick White</t>
+          <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -14023,7 +14023,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -14033,7 +14033,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Jalen Johnson</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -14043,17 +14043,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>27.5</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Onyeka Okongwu</t>
+          <t>CJ McCollum</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -14063,17 +14063,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Zaccharie Risacher</t>
+          <t>Jonathan Kuminga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -14083,17 +14083,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sam Hauser</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -14107,13 +14107,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8.5</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Dyson Daniels</t>
+          <t>Payton Pritchard</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -14127,13 +14127,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10.5</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nickeil Alexander-Walker</t>
+          <t>Derrick White</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -14143,7 +14143,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -14153,7 +14153,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Sam Hauser</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -14163,17 +14163,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>21.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CJ McCollum</t>
+          <t>Jayson Tatum</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -14183,17 +14183,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>17.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jonathan Kuminga</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -14207,7 +14207,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="27">
@@ -14353,7 +14353,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Luke Kornet</t>
+          <t>Collin Sexton</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -14363,17 +14363,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>5.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Collin Sexton</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -14383,17 +14383,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Isaac Okoro</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -14407,13 +14407,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>15.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Isaac Okoro</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -14423,17 +14423,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>8.5</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Keldon Johnson</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -14447,13 +14447,13 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>26.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Keldon Johnson</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -14463,17 +14463,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Matas Buzelis</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -14487,13 +14487,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Matas Buzelis</t>
+          <t>Luke Kornet</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -14503,11 +14503,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>18.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="42">
@@ -14527,7 +14527,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="43">
@@ -14567,7 +14567,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="45">
@@ -14607,7 +14607,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="47">
@@ -14707,7 +14707,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>20.5</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="52">
@@ -14727,7 +14727,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="53">
@@ -15167,7 +15167,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="75">
@@ -15187,7 +15187,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="76">
@@ -15227,7 +15227,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="78">
@@ -15487,7 +15487,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="91">
@@ -15687,7 +15687,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="101">

--- a/daily/2026-03-30.xlsx
+++ b/daily/2026-03-30.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00E0E0E0"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E1E2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F59E0B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF4444"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0022C55E"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -65,6 +80,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1202,7 +1220,6 @@
       <c r="V9" t="n">
         <v>4</v>
       </c>
-      <c r="W9" t="inlineStr"/>
       <c r="X9" t="n">
         <v>-6.7</v>
       </c>
@@ -1362,7 +1379,6 @@
       <c r="V11" t="n">
         <v>4</v>
       </c>
-      <c r="W11" t="inlineStr"/>
       <c r="X11" t="n">
         <v>13.8</v>
       </c>
@@ -1522,7 +1538,6 @@
       <c r="V13" t="n">
         <v>23</v>
       </c>
-      <c r="W13" t="inlineStr"/>
       <c r="X13" t="n">
         <v>10.3</v>
       </c>
@@ -2092,7 +2107,6 @@
       <c r="V20" t="n">
         <v>24</v>
       </c>
-      <c r="W20" t="inlineStr"/>
       <c r="X20" t="n">
         <v>-13.9</v>
       </c>
@@ -2826,7 +2840,6 @@
       <c r="V29" t="n">
         <v>9</v>
       </c>
-      <c r="W29" t="inlineStr"/>
       <c r="X29" t="n">
         <v>-1.6</v>
       </c>
@@ -2904,7 +2917,6 @@
       <c r="V30" t="n">
         <v>9</v>
       </c>
-      <c r="W30" t="inlineStr"/>
       <c r="X30" t="n">
         <v>-16.8</v>
       </c>
@@ -3146,7 +3158,6 @@
       <c r="V33" t="n">
         <v>2</v>
       </c>
-      <c r="W33" t="inlineStr"/>
       <c r="X33" t="n">
         <v>12.3</v>
       </c>
@@ -3470,7 +3481,6 @@
       <c r="V37" t="n">
         <v>2</v>
       </c>
-      <c r="W37" t="inlineStr"/>
       <c r="X37" t="n">
         <v>5.7</v>
       </c>
@@ -3630,7 +3640,6 @@
       <c r="V39" t="n">
         <v>2</v>
       </c>
-      <c r="W39" t="inlineStr"/>
       <c r="X39" t="n">
         <v>0</v>
       </c>
@@ -4036,7 +4045,6 @@
       <c r="V44" t="n">
         <v>6</v>
       </c>
-      <c r="W44" t="inlineStr"/>
       <c r="X44" t="n">
         <v>-10.9</v>
       </c>
@@ -4114,7 +4122,6 @@
       <c r="V45" t="n">
         <v>21</v>
       </c>
-      <c r="W45" t="inlineStr"/>
       <c r="X45" t="n">
         <v>-56</v>
       </c>
@@ -4274,7 +4281,6 @@
       <c r="V47" t="n">
         <v>21</v>
       </c>
-      <c r="W47" t="inlineStr"/>
       <c r="X47" t="n">
         <v>-3</v>
       </c>
@@ -4434,7 +4440,6 @@
       <c r="V49" t="n">
         <v>21</v>
       </c>
-      <c r="W49" t="inlineStr"/>
       <c r="X49" t="n">
         <v>6</v>
       </c>
@@ -4512,7 +4517,6 @@
       <c r="V50" t="n">
         <v>6</v>
       </c>
-      <c r="W50" t="inlineStr"/>
       <c r="X50" t="n">
         <v>-57.5</v>
       </c>
@@ -5082,7 +5086,6 @@
       <c r="V57" t="n">
         <v>16</v>
       </c>
-      <c r="W57" t="inlineStr"/>
       <c r="X57" t="n">
         <v>14.9</v>
       </c>
@@ -6390,7 +6393,6 @@
       <c r="V73" t="n">
         <v>10</v>
       </c>
-      <c r="W73" t="inlineStr"/>
       <c r="X73" t="n">
         <v>-2.4</v>
       </c>
@@ -6468,7 +6470,6 @@
       <c r="V74" t="n">
         <v>7</v>
       </c>
-      <c r="W74" t="inlineStr"/>
       <c r="X74" t="n">
         <v>-22.5</v>
       </c>
@@ -6874,7 +6875,6 @@
       <c r="V79" t="n">
         <v>10</v>
       </c>
-      <c r="W79" t="inlineStr"/>
       <c r="X79" t="n">
         <v>-12.9</v>
       </c>
@@ -6952,7 +6952,6 @@
       <c r="V80" t="n">
         <v>10</v>
       </c>
-      <c r="W80" t="inlineStr"/>
       <c r="X80" t="n">
         <v>-20.1</v>
       </c>
@@ -7030,7 +7029,6 @@
       <c r="V81" t="n">
         <v>17</v>
       </c>
-      <c r="W81" t="inlineStr"/>
       <c r="X81" t="n">
         <v>0</v>
       </c>
@@ -7108,7 +7106,6 @@
       <c r="V82" t="n">
         <v>28</v>
       </c>
-      <c r="W82" t="inlineStr"/>
       <c r="X82" t="n">
         <v>-15.5</v>
       </c>
@@ -7432,7 +7429,6 @@
       <c r="V86" t="n">
         <v>17</v>
       </c>
-      <c r="W86" t="inlineStr"/>
       <c r="X86" t="n">
         <v>-0.8</v>
       </c>
@@ -7510,7 +7506,6 @@
       <c r="V87" t="n">
         <v>17</v>
       </c>
-      <c r="W87" t="inlineStr"/>
       <c r="X87" t="n">
         <v>-0.3</v>
       </c>
@@ -7588,7 +7583,6 @@
       <c r="V88" t="n">
         <v>17</v>
       </c>
-      <c r="W88" t="inlineStr"/>
       <c r="X88" t="n">
         <v>1.4</v>
       </c>
@@ -7748,7 +7742,6 @@
       <c r="V90" t="n">
         <v>28</v>
       </c>
-      <c r="W90" t="inlineStr"/>
       <c r="X90" t="n">
         <v>-2.1</v>
       </c>
@@ -7908,7 +7901,6 @@
       <c r="V92" t="n">
         <v>20</v>
       </c>
-      <c r="W92" t="inlineStr"/>
       <c r="X92" t="n">
         <v>-11.1</v>
       </c>
@@ -7986,7 +7978,6 @@
       <c r="V93" t="n">
         <v>20</v>
       </c>
-      <c r="W93" t="inlineStr"/>
       <c r="X93" t="n">
         <v>0</v>
       </c>
@@ -8146,7 +8137,6 @@
       <c r="V95" t="n">
         <v>11</v>
       </c>
-      <c r="W95" t="inlineStr"/>
       <c r="X95" t="n">
         <v>-12.3</v>
       </c>
@@ -8388,7 +8378,6 @@
       <c r="V98" t="n">
         <v>11</v>
       </c>
-      <c r="W98" t="inlineStr"/>
       <c r="X98" t="n">
         <v>25.9</v>
       </c>
@@ -8466,7 +8455,6 @@
       <c r="V99" t="n">
         <v>20</v>
       </c>
-      <c r="W99" t="inlineStr"/>
       <c r="X99" t="n">
         <v>-3.8</v>
       </c>
@@ -13711,2023 +13699,4517 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Norman Powell</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>PHI @ MIA</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>20.5</v>
       </c>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="inlineStr"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Davion Mitchell</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>PHI @ MIA</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E3" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Mitchell scored 9 pts vs 8.5 line (+0.5), UNDER missed by 0.5 pts. Minutes were as expected: 30 played vs L10 avg 28.5. Shooting was in line with averages: 44.4% FG (4/9, L10 avg 49.2%). Counter-signals that proved correct: Volume, HR L30, HR L10, Defense. Signals that were wrong: Trend, Context, H2H. Projection model targeted 7.0 pts — actual 9 was 2.0 pts close (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Paul George</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>PHI @ MIA</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E4" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — George scored 19 pts vs 18.5 line (+0.5), UNDER missed by 0.5 pts. Minutes were as expected: 35 played vs L10 avg 32.3. Shooting efficiency was cold: 38.9% FG (-5.8% vs L10 avg of 44.7%). 7/18 from the field. Counter-signals that proved correct: Trend, Defense, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 11.1 pts — actual 19 was 7.9 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Tyrese Maxey</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>PHI @ MIA</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="4" t="n">
         <v>26.5</v>
       </c>
+      <c r="E5" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Maxey scored 23 pts vs 26.5 line (-3.5), OVER missed by 3.5 pts. Maxey played 44 min (+7.0 vs L10 avg of 36.9) — 19% more than expected. Shooting efficiency was cold: 35.0% FG (-8.5% vs L10 avg of 43.5%). 7/20 from the field. Counter-signals that proved correct: FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 28.1 pts — actual 23 was 5.1 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Bam Adebayo</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>PHI @ MIA</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="5" t="n">
         <v>21.5</v>
       </c>
+      <c r="E6" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Adebayo scored 23 pts vs 21.5 line (+1.5), OVER hit by 1.5 pts. Adebayo played 42 min (+6.2 vs L10 avg of 35.8) — 17% more than expected. Shooting efficiency was hot: 45.5% FG (+7.3% vs L10 avg of 38.2%). 5/11 from the field. Signals that called it correctly: Volume, Context, Min Trend (3/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 22.4 pts — actual 23 was 0.6 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Adebayo in this role.</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Quentin Grimes</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>PHI @ MIA</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="5" t="n">
         <v>9.5</v>
       </c>
+      <c r="E7" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Grimes scored 11 pts vs 9.5 line (+1.5), OVER hit by 1.5 pts. Minutes were as expected: 32 played vs L10 avg 33.0. Shooting was in line with averages: 50.0% FG (4/8, L10 avg 45.7%). Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (9/10 aligned). Counter-signals that were wrong: FG Trend. Projection model targeted 14.6 pts — actual 11 was 3.6 pts off (correct direction). Result classification: CLOSE_CALL. Note: Strong signal alignment (9/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Dominick Barlow</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>PHI @ MIA</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="4" t="n">
         <v>4.5</v>
       </c>
+      <c r="E8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Barlow scored 4 pts vs 4.5 line (-0.5), OVER missed by 0.5 pts. Barlow played 20 min (-4.2 vs L10 avg of 23.9) — 18% less than expected. Shooting efficiency was hot: 100.0% FG (+49.4% vs L10 avg of 50.6%). 2/2 from the field. Counter-signals that proved correct: Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 8.6 pts — actual 4 was 4.6 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Barlow for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Joel Embiid</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>PHI @ MIA</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="5" t="n">
         <v>28.5</v>
       </c>
+      <c r="E9" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Embiid scored 26 pts vs 28.5 line (-2.5), UNDER hit by 2.5 pts. Minutes were as expected: 34 played vs L10 avg 32.9. Shooting efficiency was cold: 40.0% FG (-13.1% vs L10 avg of 53.1%). 10/25 from the field. Signals that called it correctly: Volume, Context, Defense (3/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 23.2 pts — actual 26 was 2.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Embiid's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Kelly Oubre Jr.</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>PHI @ MIA</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="5" t="n">
         <v>9.5</v>
       </c>
+      <c r="E10" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Jr. scored 11 pts vs 9.5 line (+1.5), OVER hit by 1.5 pts. Minutes were as expected: 31 played vs L10 avg 31.2. Shooting efficiency was cold: 35.7% FG (-8.8% vs L10 avg of 44.5%). 5/14 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (9/10 aligned). Counter-signals that were wrong: Min Trend. Projection model targeted 12.9 pts — actual 11 was 1.9 pts close (correct direction). Result classification: CLOSE_CALL. Note: Strong signal alignment (9/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>VJ Edgecombe</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>PHI @ MIA</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E11" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Edgecombe scored 13 pts vs 13.5 line (-0.5), OVER missed by 0.5 pts. Edgecombe played 30 min (-3.5 vs L10 avg of 33.4) — 10% less than expected. Shooting efficiency was hot: 62.5% FG (+16.4% vs L10 avg of 46.1%). 5/8 from the field. Counter-signals that proved correct: H2H, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 20.3 pts — actual 13 was 7.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Tyler Herro</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>PHI @ MIA</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="5" t="n">
         <v>21.5</v>
       </c>
+      <c r="E12" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Herro scored 30 pts vs 21.5 line (+8.5), OVER hit by 8.5 pts. Herro played 42 min (+9.4 vs L10 avg of 32.5) — 29% more than expected. Shooting was in line with averages: 50.0% FG (12/24, L10 avg 46.1%). Signals that called it correctly: Volume, HR L30, Context, Defense, H2H (6/10 aligned). Counter-signals that were wrong: HR L10, Trend, Pace. Projection model targeted 23.2 pts — actual 30 was 6.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Herro's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Andrew Wiggins</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>PHI @ MIA</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E13" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Wiggins scored 14 pts vs 13.5 line (+0.5), UNDER missed by 0.5 pts. Wiggins played 36 min (+8.2 vs L10 avg of 27.5) — 30% more than expected. Shooting efficiency was cold: 46.2% FG (-6.4% vs L10 avg of 52.6%). 6/13 from the field. Counter-signals that proved correct: Volume, HR L30, Context, Defense. Signals that were wrong: HR L10, Trend, Pace. Projection model targeted 12.7 pts — actual 14 was 1.3 pts close (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Onyeka Okongwu</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>BOS @ ATL</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="5" t="n">
         <v>12.5</v>
       </c>
+      <c r="E14" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Okongwu scored 20 pts vs 12.5 line (+7.5), OVER hit by 7.5 pts. Okongwu played 36 min (+7.5 vs L10 avg of 28.8) — 26% more than expected. Shooting was in line with averages: 50.0% FG (7/14, L10 avg 46.5%). Signals that called it correctly: Volume, HR L30, Context, H2H (4/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 13.7 pts — actual 20 was 6.3 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Okongwu's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Zaccharie Risacher</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>BOS @ ATL</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="5" t="n">
         <v>5.5</v>
       </c>
+      <c r="E15" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Risacher scored 9 pts vs 5.5 line (+3.5), OVER hit by 3.5 pts. Risacher played 16 min (-3.1 vs L10 avg of 18.7) — 17% less than expected. Shooting efficiency was hot: 75.0% FG (+22.3% vs L10 avg of 52.7%). 3/4 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, Pace, Min Trend. Projection model targeted 6.2 pts — actual 9 was 2.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Risacher's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Dyson Daniels</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>BOS @ ATL</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="5" t="n">
         <v>10.5</v>
       </c>
+      <c r="E16" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Daniels scored 18 pts vs 10.5 line (+7.5), OVER hit by 7.5 pts. Daniels played 38 min (+5.1 vs L10 avg of 32.4) — 16% more than expected. Shooting efficiency was hot: 72.7% FG (+16.9% vs L10 avg of 55.8%). 8/11 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: Defense, Pace. Projection model targeted 14.8 pts — actual 18 was 3.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>BOS @ ATL</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="4" t="n">
         <v>17.5</v>
       </c>
+      <c r="E17" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Alexander-Walker scored 17 pts vs 17.5 line (-0.5), OVER missed by 0.5 pts. Minutes were as expected: 35 played vs L10 avg 33.2. Shooting efficiency was cold: 37.5% FG (-14.1% vs L10 avg of 51.6%). 6/16 from the field. Counter-signals that proved correct: Defense, H2H, Pace, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 18.6 pts — actual 17 was 1.6 pts close (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Jalen Johnson</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>BOS @ ATL</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="5" t="n">
         <v>21.5</v>
       </c>
+      <c r="E18" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Johnson scored 20 pts vs 21.5 line (-1.5), UNDER hit by 1.5 pts. Minutes were as expected: 36 played vs L10 avg 37.0. Shooting was in line with averages: 53.8% FG (7/13, L10 avg 50.0%). Signals that called it correctly: Context, Defense, H2H, Pace (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 20.0 pts — actual 20 was 0.0 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Johnson in this role.</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>CJ McCollum</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>BOS @ ATL</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="5" t="n">
         <v>17.5</v>
       </c>
+      <c r="E19" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>WIN — McCollum scored 14 pts vs 17.5 line (-3.5), UNDER hit by 3.5 pts. Minutes were as expected: 30 played vs L10 avg 29.2. Shooting efficiency was cold: 35.3% FG (-13.6% vs L10 avg of 48.9%). 6/17 from the field. Signals that called it correctly: Defense, H2H, Pace (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 14.1 pts — actual 14 was 0.1 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for McCollum in this role.</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Jonathan Kuminga</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>BOS @ ATL</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E20" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Kuminga scored 10 pts vs 7.5 line (+2.5), UNDER missed by 2.5 pts. Minutes were as expected: 23 played vs L10 avg 21.5. Shooting was in line with averages: 36.4% FG (4/11, L10 avg 40.9%). Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, Defense, Pace. Projection model targeted 4.3 pts — actual 10 was 5.7 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Kuminga's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Jaylen Brown</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>BOS @ ATL</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="5" t="n">
         <v>27.5</v>
       </c>
+      <c r="E21" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Brown scored 29 pts vs 27.5 line (+1.5), OVER hit by 1.5 pts. Brown played 40 min (+5.7 vs L10 avg of 34.4) — 17% more than expected. Shooting efficiency was cold: 31.0% FG (-15.6% vs L10 avg of 46.6%). 9/29 from the field. Signals that called it correctly: HR L10, Trend, Context, Defense, H2H (7/10 aligned). Counter-signals that were wrong: Volume, HR L30, Min Trend. Projection model targeted 28.7 pts — actual 29 was 0.3 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Brown in this role.</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Payton Pritchard</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>BOS @ ATL</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E22" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Pritchard scored 16 pts vs 18.5 line (-2.5), OVER missed by 2.5 pts. Pritchard played 26 min (-8.0 vs L10 avg of 33.6) — 24% less than expected. Shooting was in line with averages: 42.9% FG (6/14, L10 avg 44.0%). Counter-signals that proved correct: Volume, HR L10, H2H. Signals that were wrong: HR L30, Trend, Context. Projection model targeted 21.4 pts — actual 16 was 5.4 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Pritchard for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Derrick White</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>BOS @ ATL</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="5" t="n">
         <v>17.5</v>
       </c>
+      <c r="E23" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>WIN — White scored 7 pts vs 17.5 line (-10.5), UNDER hit by 10.5 pts. Minutes were as expected: 36 played vs L10 avg 34.1. Shooting efficiency was cold: 25.0% FG (-13.0% vs L10 avg of 38.0%). 3/12 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, Pace, FG Trend. Projection model targeted 15.3 pts — actual 7 was 8.3 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms White's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Sam Hauser</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>BOS @ ATL</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E24" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Hauser scored 7 pts vs 8.5 line (-1.5), OVER missed by 1.5 pts. Hauser played 21 min (-5.2 vs L10 avg of 26.2) — 20% less than expected. Shooting efficiency was hot: 40.0% FG (+6.2% vs L10 avg of 33.8%). 2/5 from the field. Counter-signals that proved correct: HR L10, Trend, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 9.4 pts — actual 7 was 2.4 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Hauser for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Jayson Tatum</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>BOS @ ATL</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="3" t="n">
         <v>20.5</v>
       </c>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="n"/>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Neemias Queta</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>BOS @ ATL</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="inlineStr"/>
+      <c r="I26" s="3" t="n"/>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>Harrison Barnes</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>CHI @ SAS</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="5" t="n">
         <v>7.5</v>
       </c>
+      <c r="E27" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Barnes scored 3 pts vs 7.5 line (-4.5), UNDER hit by 4.5 pts. Barnes played 17 min (-4.1 vs L10 avg of 21.4) — 19% less than expected. Shooting efficiency was cold: 20.0% FG (-27.9% vs L10 avg of 47.9%). 1/5 from the field. Signals that called it correctly: Context, Min Trend (2/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 5.2 pts — actual 3 was 2.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Barnes's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>Devin Vassell</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>CHI @ SAS</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="5" t="n">
         <v>13.5</v>
       </c>
+      <c r="E28" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Vassell scored 6 pts vs 13.5 line (-7.5), UNDER hit by 7.5 pts. Minutes were as expected: 31 played vs L10 avg 30.3. Shooting efficiency was cold: 22.2% FG (-19.6% vs L10 avg of 41.8%). 2/9 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H, FG Trend (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 6.9 pts — actual 6 was 0.9 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Vassell in this role.</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Tre Jones</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>CHI @ SAS</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="5" t="n">
         <v>13.5</v>
       </c>
+      <c r="E29" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Jones scored 23 pts vs 13.5 line (+9.5), OVER hit by 9.5 pts. Jones played 26 min (-3.3 vs L10 avg of 29.0) — 11% less than expected. Shooting efficiency was hot: 69.2% FG (+13.1% vs L10 avg of 56.1%). 9/13 from the field. Signals that called it correctly: Volume, HR L10, Trend, Context, Pace (7/10 aligned). Counter-signals that were wrong: HR L30, Defense, H2H. Projection model targeted 20.3 pts — actual 23 was 2.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Jones's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Josh Giddey</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>CHI @ SAS</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="5" t="n">
         <v>16.5</v>
       </c>
+      <c r="E30" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Giddey scored 9 pts vs 16.5 line (-7.5), UNDER hit by 7.5 pts. Giddey played 33 min (-3.0 vs L10 avg of 36.0) — 8% less than expected. Shooting efficiency was hot: 60.0% FG (+18.6% vs L10 avg of 41.4%). 3/5 from the field. Signals that called it correctly: Volume, HR L30, Trend, Context, Defense (5/10 aligned). Counter-signals that were wrong: HR L10, H2H, Pace. Projection model targeted 6.8 pts — actual 9 was 2.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Giddey's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Julian Champagnie</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>CHI @ SAS</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E31" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Champagnie scored 13 pts vs 10.5 line (+2.5), UNDER missed by 2.5 pts. Minutes were as expected: 28 played vs L10 avg 26.7. Shooting efficiency was hot: 71.4% FG (+31.7% vs L10 avg of 39.7%). 5/7 from the field. Counter-signals that proved correct: Defense, Pace, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 7.4 pts — actual 13 was 5.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Nick Richards</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>CHI @ SAS</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="inlineStr"/>
+      <c r="I32" s="3" t="n"/>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>De'Aaron Fox</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>CHI @ SAS</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="4" t="n">
         <v>16.5</v>
       </c>
+      <c r="E33" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Fox scored 7 pts vs 16.5 line (-9.5), OVER missed by 9.5 pts. Fox played 23 min (-6.6 vs L10 avg of 29.8) — 22% less than expected. Shooting efficiency was cold: 37.5% FG (-14.3% vs L10 avg of 51.8%). 3/8 from the field. Counter-signals that proved correct: HR L30, Trend, H2H. Signals that were wrong: Volume, HR L10, Context. Projection model targeted 17.1 pts — actual 7 was 10.1 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Fox for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>Collin Sexton</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>CHI @ SAS</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="5" t="n">
         <v>16.5</v>
       </c>
+      <c r="E34" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Sexton scored 20 pts vs 16.5 line (+3.5), OVER hit by 3.5 pts. Minutes were as expected: 27 played vs L10 avg 26.3. Shooting was in line with averages: 53.3% FG (8/15, L10 avg 52.3%). Signals that called it correctly: HR L10, Trend, H2H, Pace, FG Trend (6/10 aligned). Counter-signals that were wrong: Volume, HR L30, Context. Projection model targeted 19.6 pts — actual 20 was 0.4 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Sexton in this role.</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Stephon Castle</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>CHI @ SAS</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E35" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Castle scored 21 pts vs 15.5 line (+5.5), UNDER missed by 5.5 pts. Castle played 35 min (+5.3 vs L10 avg of 29.3) — 18% more than expected. Shooting was in line with averages: 50.0% FG (6/12, L10 avg 46.8%). Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Context, H2H, FG Trend. Projection model targeted 14.6 pts — actual 21 was 6.4 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Castle's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>Isaac Okoro</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>CHI @ SAS</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="5" t="n">
         <v>8.5</v>
       </c>
+      <c r="E36" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Okoro scored 6 pts vs 8.5 line (-2.5), UNDER hit by 2.5 pts. Okoro played 25 min (-5.3 vs L10 avg of 30.5) — 17% less than expected. Shooting was in line with averages: 40.0% FG (2/5, L10 avg 38.7%). Signals that called it correctly: Defense, H2H, FG Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 7.0 pts — actual 6 was 1.0 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Okoro in this role.</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>Victor Wembanyama</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>CHI @ SAS</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="5" t="n">
         <v>26.5</v>
       </c>
+      <c r="E37" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Wembanyama scored 41 pts vs 26.5 line (+14.5), OVER hit by 14.5 pts. Minutes were as expected: 30 played vs L10 avg 29.9. Shooting efficiency was hot: 63.0% FG (+12.6% vs L10 avg of 50.4%). 17/27 from the field. Signals that called it correctly: Trend, Defense, Pace, FG Trend (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 30.2 pts — actual 41 was 10.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Wembanyama's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>Keldon Johnson</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>CHI @ SAS</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="5" t="n">
         <v>12.5</v>
       </c>
+      <c r="E38" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Johnson scored 15 pts vs 12.5 line (+2.5), OVER hit by 2.5 pts. Johnson played 26 min (+4.1 vs L10 avg of 22.4) — 18% more than expected. Shooting efficiency was cold: 45.5% FG (-6.0% vs L10 avg of 51.5%). 5/11 from the field. Signals that called it correctly: Volume, HR L10, Trend, Context, Defense (9/10 aligned). Counter-signals that were wrong: HR L30. Projection model targeted 15.7 pts — actual 15 was 0.7 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (9/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>Dylan Harper</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>CHI @ SAS</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="5" t="n">
         <v>13.5</v>
       </c>
+      <c r="E39" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Harper scored 13 pts vs 13.5 line (-0.5), UNDER hit by 0.5 pts. Minutes were as expected: 24 played vs L10 avg 23.9. Shooting was in line with averages: 54.5% FG (6/11, L10 avg 58.1%). Signals that called it correctly: Volume, HR L30, Context (3/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 12.9 pts — actual 13 was 0.1 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Harper in this role.</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>Matas Buzelis</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>CHI @ SAS</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="5" t="n">
         <v>17.5</v>
       </c>
+      <c r="E40" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Buzelis scored 12 pts vs 17.5 line (-5.5), UNDER hit by 5.5 pts. Buzelis played 28 min (-6.8 vs L10 avg of 34.8) — 20% less than expected. Shooting was in line with averages: 41.7% FG (5/12, L10 avg 44.4%). Signals that called it correctly: Defense, H2H (2/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 16.8 pts — actual 12 was 4.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Buzelis's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>Luke Kornet</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>CHI @ SAS</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="5" t="n">
         <v>3.5</v>
       </c>
+      <c r="E41" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Kornet scored 10 pts vs 3.5 line (+6.5), OVER hit by 6.5 pts. Minutes were as expected: 19 played vs L10 avg 19.0. Shooting efficiency was hot: 80.0% FG (+32.8% vs L10 avg of 47.2%). 4/5 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (8/10 aligned). Counter-signals that were wrong: Trend, FG Trend. Projection model targeted 3.4 pts — actual 10 was 6.6 pts off (wrong direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>Collin Gillespie</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>PHX @ MEM</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="5" t="n">
         <v>12.5</v>
       </c>
+      <c r="E42" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Gillespie scored 11 pts vs 12.5 line (-1.5), UNDER hit by 1.5 pts. Gillespie played 32 min (+3.4 vs L10 avg of 28.8) — 12% more than expected. Shooting efficiency was cold: 25.0% FG (-7.4% vs L10 avg of 32.4%). 4/16 from the field. Signals that called it correctly: HR L30, HR L10, Context, H2H, FG Trend (6/10 aligned). Counter-signals that were wrong: Volume, Trend, Defense. Projection model targeted 8.0 pts — actual 11 was 3.0 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Gillespie's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Royce O'Neale</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>PHX @ MEM</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E43" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — O'Neale scored 9 pts vs 9.5 line (-0.5), OVER missed by 0.5 pts. Minutes were as expected: 24 played vs L10 avg 26.7. Shooting was in line with averages: 42.9% FG (3/7, L10 avg 40.7%). Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Context, Defense, H2H. Projection model targeted 11.8 pts — actual 9 was 2.8 pts off (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>Jordan Goodwin</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>PHX @ MEM</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="5" t="n">
         <v>9.5</v>
       </c>
+      <c r="E44" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Goodwin scored 9 pts vs 9.5 line (-0.5), UNDER hit by 0.5 pts. Goodwin played 28 min (+4.8 vs L10 avg of 23.4) — 21% more than expected. Shooting efficiency was cold: 33.3% FG (-10.3% vs L10 avg of 43.6%). 3/9 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context (4/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 5.7 pts — actual 9 was 3.3 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Goodwin's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>Taylor Hendricks</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>PHX @ MEM</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="5" t="n">
         <v>11.5</v>
       </c>
+      <c r="E45" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Hendricks scored 5 pts vs 11.5 line (-6.5), UNDER hit by 6.5 pts. Hendricks played 18 min (-8.5 vs L10 avg of 26.2) — 32% less than expected. Shooting was in line with averages: 40.0% FG (2/5, L10 avg 41.1%). Signals that called it correctly: Volume, HR L30, Trend, Context, Defense (7/10 aligned). Counter-signals that were wrong: HR L10, H2H, Min Trend. Projection model targeted 1.6 pts — actual 5 was 3.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Hendricks's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>Grayson Allen</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>PHX @ MEM</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E46" s="3" t="n"/>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="inlineStr"/>
+      <c r="I46" s="3" t="n"/>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Walter Clayton Jr.</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>PHX @ MEM</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E47" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Jr. scored 11 pts vs 10.5 line (+0.5), UNDER missed by 0.5 pts. Jr. played 30 min (+5.2 vs L10 avg of 24.4) — 21% more than expected. Shooting efficiency was hot: 66.7% FG (+37.9% vs L10 avg of 28.8%). 4/6 from the field. Counter-signals that proved correct: Trend, H2H, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 5.4 pts — actual 11 was 5.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>Oso Ighodaro</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>PHX @ MEM</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E48" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Ighodaro scored 11 pts vs 9.5 line (+1.5), UNDER missed by 1.5 pts. Ighodaro played 35 min (+5.6 vs L10 avg of 29.1) — 19% more than expected. Shooting efficiency was cold: 55.6% FG (-16.0% vs L10 avg of 71.6%). 5/9 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, Pace. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 4.1 pts — actual 11 was 6.9 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>Cedric Coward</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>PHX @ MEM</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="5" t="n">
         <v>14.5</v>
       </c>
+      <c r="E49" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Coward scored 7 pts vs 14.5 line (-7.5), UNDER hit by 7.5 pts. Minutes were as expected: 24 played vs L10 avg 22.9. Shooting efficiency was cold: 14.3% FG (-33.0% vs L10 avg of 47.3%). 1/7 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, Pace (7/10 aligned). Counter-signals that were wrong: HR L10, Trend, H2H. Projection model targeted 12.4 pts — actual 7 was 5.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Coward's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>Khaman Maluach</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>PHX @ MEM</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="4" t="n">
         <v>5.5</v>
       </c>
+      <c r="E50" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Maluach scored 6 pts vs 5.5 line (+0.5), UNDER missed by 0.5 pts. Minutes were as expected: 13 played vs L10 avg 13.5. Shooting was in line with averages: 50.0% FG (2/4, L10 avg 50.1%). Counter-signals that proved correct: Trend, Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted -0.2 pts — actual 6 was 6.2 pts off (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>Jalen Green</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>PHX @ MEM</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="E51" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Green scored 21 pts vs 22.5 line (-1.5), OVER missed by 1.5 pts. Green played 24 min (-6.9 vs L10 avg of 31.3) — 22% less than expected. Shooting was in line with averages: 50.0% FG (9/18, L10 avg 46.7%). Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, Defense, H2H. Projection model targeted 26.4 pts — actual 21 was 5.4 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Green for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>Devin Booker</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>PHX @ MEM</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="4" t="n">
         <v>26.5</v>
       </c>
+      <c r="E52" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Booker scored 36 pts vs 26.5 line (+9.5), UNDER missed by 9.5 pts. Booker played 26 min (-7.9 vs L10 avg of 33.7) — 23% less than expected. Shooting efficiency was hot: 66.7% FG (+20.7% vs L10 avg of 46.0%). 16/24 from the field. Counter-signals that proved correct: HR L30, HR L10, Defense, Pace. Signals that were wrong: Volume, Trend, Context. Projection model targeted 24.1 pts — actual 36 was 11.9 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Booker for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>GG Jackson</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>PHX @ MEM</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="5" t="n">
         <v>17.5</v>
       </c>
+      <c r="E53" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Jackson scored 14 pts vs 17.5 line (-3.5), UNDER hit by 3.5 pts. Jackson played 17 min (-9.6 vs L10 avg of 26.5) — 36% less than expected. Shooting efficiency was hot: 85.7% FG (+40.7% vs L10 avg of 45.0%). 6/7 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, H2H (7/10 aligned). Counter-signals that were wrong: HR L10, Trend, Min Trend. Projection model targeted 14.5 pts — actual 14 was 0.5 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Jackson in this role.</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>Max Christie</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>MIN @ DAL</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="5" t="n">
         <v>9.5</v>
       </c>
+      <c r="E54" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Christie scored 3 pts vs 9.5 line (-6.5), UNDER hit by 6.5 pts. Minutes were as expected: 28 played vs L10 avg 28.1. Shooting efficiency was cold: 20.0% FG (-28.9% vs L10 avg of 48.9%). 1/5 from the field. Signals that called it correctly: Trend, Defense, H2H, Pace, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 4.8 pts — actual 3 was 1.8 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Christie in this role.</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>Marvin Bagley III</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>MIN @ DAL</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E55" s="3" t="n"/>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="inlineStr"/>
+      <c r="I55" s="3" t="n"/>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>Donte DiVincenzo</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>MIN @ DAL</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E56" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — DiVincenzo scored 15 pts vs 12.5 line (+2.5), UNDER missed by 2.5 pts. Minutes were as expected: 30 played vs L10 avg 30.4. Shooting efficiency was hot: 45.5% FG (+9.5% vs L10 avg of 36.0%). 5/11 from the field. Counter-signals that proved correct: Trend, Defense, Pace, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 8.0 pts — actual 15 was 7.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>Cooper Flagg</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>MIN @ DAL</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="5" t="n">
         <v>22.5</v>
       </c>
+      <c r="E57" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Flagg scored 12 pts vs 22.5 line (-10.5), UNDER hit by 10.5 pts. Flagg played 31 min (-3.9 vs L10 avg of 34.6) — 11% less than expected. Shooting efficiency was cold: 26.3% FG (-21.8% vs L10 avg of 48.1%). 5/19 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, Pace (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, H2H. Projection model targeted 16.3 pts — actual 12 was 4.3 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Flagg's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>P.J. Washington</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>MIN @ DAL</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E58" s="3" t="n"/>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="inlineStr"/>
+      <c r="I58" s="3" t="n"/>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>Anthony Edwards</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>MIN @ DAL</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="4" t="n">
         <v>28.5</v>
       </c>
+      <c r="E59" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Edwards scored 17 pts vs 28.5 line (-11.5), OVER missed by 11.5 pts. Edwards played 23 min (-13.0 vs L10 avg of 35.6) — 37% less than expected. Shooting efficiency was hot: 53.8% FG (+6.5% vs L10 avg of 47.3%). 7/13 from the field. Counter-signals that proved correct: Trend, H2H, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 28.4 pts — actual 17 was 11.4 pts off (wrong direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Edwards for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>Naji Marshall</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>MIN @ DAL</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="inlineStr"/>
+      <c r="I60" s="3" t="n"/>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>Brandon Williams</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>MIN @ DAL</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" s="5" t="n">
         <v>10.5</v>
       </c>
+      <c r="E61" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Williams scored 15 pts vs 10.5 line (+4.5), OVER hit by 4.5 pts. Williams played 28 min (+7.8 vs L10 avg of 20.0) — 39% more than expected. Shooting was in line with averages: 40.0% FG (4/10, L10 avg 43.0%). Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (5/10 aligned). Counter-signals that were wrong: Trend, Defense, Pace. Projection model targeted 10.4 pts — actual 15 was 4.6 pts off (wrong direction). Result classification: MODEL_CORRECT. Note: Result confirms Williams's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="4" t="inlineStr">
         <is>
           <t>Ayo Dosunmu</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>MIN @ DAL</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="4" t="n">
         <v>16.5</v>
       </c>
+      <c r="E62" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Dosunmu scored 18 pts vs 16.5 line (+1.5), UNDER missed by 1.5 pts. Dosunmu played 33 min (+4.0 vs L10 avg of 29.2) — 14% more than expected. Shooting efficiency was hot: 61.5% FG (+7.9% vs L10 avg of 53.6%). 8/13 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, Pace. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 10.4 pts — actual 18 was 7.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>Klay Thompson</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="5" t="inlineStr">
         <is>
           <t>MIN @ DAL</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="5" t="n">
         <v>9.5</v>
       </c>
+      <c r="E63" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Thompson scored 5 pts vs 9.5 line (-4.5), UNDER hit by 4.5 pts. Minutes were as expected: 22 played vs L10 avg 21.5. Shooting efficiency was cold: 12.5% FG (-32.1% vs L10 avg of 44.6%). 1/8 from the field. Signals that called it correctly: Trend, Defense, H2H, Pace, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 8.0 pts — actual 5 was 3.0 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Thompson's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t>Daniel Gafford</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>MIN @ DAL</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="5" t="n">
         <v>10.5</v>
       </c>
+      <c r="E64" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Gafford scored 21 pts vs 10.5 line (+10.5), OVER hit by 10.5 pts. Minutes were as expected: 24 played vs L10 avg 24.3. Shooting efficiency was hot: 81.8% FG (+8.2% vs L10 avg of 73.6%). 9/11 from the field. Signals that called it correctly: Volume, HR L10, Trend, Context, FG Trend (6/10 aligned). Counter-signals that were wrong: HR L30, Defense, H2H. Projection model targeted 10.4 pts — actual 21 was 10.6 pts off (wrong direction). Result classification: MODEL_CORRECT. Note: Result confirms Gafford's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>Rudy Gobert</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>MIN @ DAL</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E65" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Gobert scored 14 pts vs 12.5 line (+1.5), UNDER missed by 1.5 pts. Minutes were as expected: 28 played vs L10 avg 30.8. Shooting efficiency was hot: 75.0% FG (+18.7% vs L10 avg of 56.3%). 6/8 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, H2H. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 11.2 pts — actual 14 was 2.8 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t>Julius Randle</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>MIN @ DAL</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="4" t="n">
         <v>21.5</v>
       </c>
+      <c r="E66" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Randle scored 24 pts vs 21.5 line (+2.5), UNDER missed by 2.5 pts. Minutes were as expected: 31 played vs L10 avg 31.5. Shooting efficiency was hot: 64.3% FG (+21.7% vs L10 avg of 42.6%). 9/14 from the field. Counter-signals that proved correct: Defense, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 16.8 pts — actual 24 was 7.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>Naz Reid</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>MIN @ DAL</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="5" t="n">
         <v>14.5</v>
       </c>
+      <c r="E67" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Reid scored 12 pts vs 14.5 line (-2.5), UNDER hit by 2.5 pts. Minutes were as expected: 25 played vs L10 avg 25.2. Shooting efficiency was cold: 35.7% FG (-7.0% vs L10 avg of 42.7%). 5/14 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (6/10 aligned). Counter-signals that were wrong: Defense, H2H, Pace. Projection model targeted 14.6 pts — actual 12 was 2.6 pts off (wrong direction). Result classification: MODEL_CORRECT. Note: Result confirms Reid's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>Khris Middleton</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>MIN @ DAL</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="5" t="n">
         <v>8.5</v>
       </c>
+      <c r="E68" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Middleton scored 9 pts vs 8.5 line (+0.5), OVER hit by 0.5 pts. Middleton played 23 min (+3.6 vs L10 avg of 19.0) — 19% more than expected. Shooting was in line with averages: 40.0% FG (4/10, L10 avg 37.8%). Signals that called it correctly: Volume, HR L30, Context, H2H (4/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 13.2 pts — actual 9 was 4.2 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Middleton's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="5" t="inlineStr">
         <is>
           <t>Brice Sensabaugh</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>CLE @ UTA</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="5" t="n">
         <v>20.5</v>
       </c>
+      <c r="E69" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Sensabaugh scored 18 pts vs 20.5 line (-2.5), UNDER hit by 2.5 pts. Minutes were as expected: 26 played vs L10 avg 28.1. Shooting was in line with averages: 50.0% FG (6/12, L10 avg 49.9%). Signals that called it correctly: Volume, HR L30, Context, H2H (4/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 11.3 pts — actual 18 was 6.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Sensabaugh's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="4" t="inlineStr">
         <is>
           <t>Sam Merrill</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t>CLE @ UTA</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E70" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Merrill scored 9 pts vs 14.5 line (-5.5), OVER missed by 5.5 pts. Minutes were as expected: 28 played vs L10 avg 28.6. Shooting efficiency was cold: 28.6% FG (-12.7% vs L10 avg of 41.3%). 4/14 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, Defense, Pace. Projection model targeted 16.3 pts — actual 9 was 7.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>James Harden</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>CLE @ UTA</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="4" t="n">
         <v>20.5</v>
       </c>
+      <c r="E71" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Harden scored 13 pts vs 20.5 line (-7.5), OVER missed by 7.5 pts. Harden played 39 min (+3.7 vs L10 avg of 34.9) — 11% more than expected. Shooting efficiency was cold: 44.4% FG (-5.4% vs L10 avg of 49.8%). 4/9 from the field. Counter-signals that proved correct: HR L30, HR L10. Signals that were wrong: Volume, Trend, Context. Projection model targeted 21.4 pts — actual 13 was 8.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>Evan Mobley</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>CLE @ UTA</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E72" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Mobley scored 34 pts vs 18.5 line (+15.5), UNDER missed by 15.5 pts. Minutes were as expected: 30 played vs L10 avg 31.1. Shooting efficiency was hot: 71.4% FG (+5.3% vs L10 avg of 66.1%). 15/21 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, Pace. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 15.7 pts — actual 34 was 18.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>Ace Bailey</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>CLE @ UTA</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E73" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Bailey scored 19 pts vs 18.5 line (+0.5), UNDER missed by 0.5 pts. Bailey played 35 min (+6.1 vs L10 avg of 28.9) — 21% more than expected. Shooting efficiency was hot: 53.3% FG (+5.0% vs L10 avg of 48.3%). 8/15 from the field. Counter-signals that proved correct: Trend, Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 7.1 pts — actual 19 was 11.9 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>Thomas Bryant</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>CLE @ UTA</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="5" t="n">
         <v>8.5</v>
       </c>
+      <c r="E74" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Bryant scored 2 pts vs 8.5 line (-6.5), UNDER hit by 6.5 pts. Bryant played 18 min (+3.4 vs L10 avg of 15.0) — 23% more than expected. Shooting efficiency was cold: 33.3% FG (-24.5% vs L10 avg of 57.8%). 1/3 from the field. Signals that called it correctly: Volume, HR L30, Context (3/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 5.3 pts — actual 2 was 3.3 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Bryant's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>Kyle Filipowski</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>CLE @ UTA</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E75" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Filipowski scored 20 pts vs 13.5 line (+6.5), UNDER missed by 6.5 pts. Minutes were as expected: 24 played vs L10 avg 26.2. Shooting efficiency was hot: 58.3% FG (+11.3% vs L10 avg of 47.0%). 7/12 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, Pace. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 11.7 pts — actual 20 was 8.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>Donovan Mitchell</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>CLE @ UTA</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" s="4" t="n">
         <v>26.5</v>
       </c>
+      <c r="E76" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Mitchell scored 34 pts vs 26.5 line (+7.5), UNDER missed by 7.5 pts. Minutes were as expected: 36 played vs L10 avg 34.0. Shooting efficiency was hot: 55.6% FG (+12.6% vs L10 avg of 43.0%). 10/18 from the field. Counter-signals that proved correct: Defense, Pace, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 17.8 pts — actual 34 was 16.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>Keon Ellis</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>CLE @ UTA</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E77" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Ellis scored 13 pts vs 9.5 line (+3.5), UNDER missed by 3.5 pts. Ellis played 32 min (+5.0 vs L10 avg of 26.9) — 19% more than expected. Shooting was in line with averages: 60.0% FG (6/10, L10 avg 57.0%). Counter-signals that proved correct: HR L10, Trend, Defense, Pace. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 5.8 pts — actual 13 was 7.2 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Ellis's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t>Dennis Schröder</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="4" t="inlineStr">
         <is>
           <t>CLE @ UTA</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D78" t="n">
+      <c r="D78" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E78" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Schröder scored 3 pts vs 9.5 line (-6.5), OVER missed by 6.5 pts. Minutes were as expected: 21 played vs L10 avg 19.2. Shooting efficiency was cold: 25.0% FG (-11.5% vs L10 avg of 36.5%). 1/4 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Context, Defense, H2H. Projection model targeted 10.0 pts — actual 3 was 7.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>Cody Williams</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>CLE @ UTA</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D79" t="n">
+      <c r="D79" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E79" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Williams scored 26 pts vs 12.5 line (+13.5), UNDER missed by 13.5 pts. Minutes were as expected: 37 played vs L10 avg 33.8. Shooting was in line with averages: 50.0% FG (11/22, L10 avg 48.8%). Counter-signals that proved correct: HR L10, Trend, Defense, H2H. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 9.9 pts — actual 26 was 16.1 pts off (correct direction). Loss classification: BLOWOUT_EFFECT. Note: Game script invalidated the prop. Consider blowout probability when UTA is involved.</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="4" t="inlineStr">
         <is>
           <t>John Konchar</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t>CLE @ UTA</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" s="4" t="n">
         <v>4.5</v>
       </c>
+      <c r="E80" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Konchar scored 6 pts vs 4.5 line (+1.5), UNDER missed by 1.5 pts. Konchar played 30 min (+3.4 vs L10 avg of 26.6) — 13% more than expected. Shooting efficiency was hot: 50.0% FG (+11.2% vs L10 avg of 38.8%). 2/4 from the field. Counter-signals that proved correct: Volume, Trend, H2H, Pace. Signals that were wrong: HR L30, HR L10, Context. Projection model targeted 2.6 pts — actual 6 was 3.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="5" t="inlineStr">
         <is>
           <t>Ajay Mitchell</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>DET @ OKC</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D81" t="n">
+      <c r="D81" s="5" t="n">
         <v>14.5</v>
       </c>
+      <c r="E81" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Mitchell scored 14 pts vs 14.5 line (-0.5), UNDER hit by 0.5 pts. Mitchell played 36 min (+10.7 vs L10 avg of 25.2) — 42% more than expected. Shooting efficiency was cold: 40.0% FG (-12.6% vs L10 avg of 52.6%). 4/10 from the field. Signals that called it correctly: Volume, HR L30, Trend, Context, Defense (7/10 aligned). Counter-signals that were wrong: HR L10, H2H, FG Trend. Projection model targeted 12.8 pts — actual 14 was 1.2 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Mitchell in this role.</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="5" t="inlineStr">
         <is>
           <t>Daniss Jenkins</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="5" t="inlineStr">
         <is>
           <t>DET @ OKC</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D82" t="n">
+      <c r="D82" s="5" t="n">
         <v>16.5</v>
       </c>
+      <c r="E82" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Jenkins scored 15 pts vs 16.5 line (-1.5), UNDER hit by 1.5 pts. Jenkins played 36 min (+6.2 vs L10 avg of 30.1) — 21% more than expected. Shooting was in line with averages: 41.2% FG (7/17, L10 avg 44.1%). Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (6/10 aligned). Counter-signals that were wrong: Trend, H2H, FG Trend. Projection model targeted 5.1 pts — actual 15 was 9.9 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Jenkins's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="4" t="inlineStr">
         <is>
           <t>Kevin Huerter</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t>DET @ OKC</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D83" t="n">
+      <c r="D83" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E83" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Huerter scored 17 pts vs 11.5 line (+5.5), UNDER missed by 5.5 pts. Huerter played 38 min (+15.6 vs L10 avg of 22.7) — 69% more than expected. Shooting was in line with averages: 43.8% FG (7/16, L10 avg 44.4%). Counter-signals that proved correct: Trend, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 0.5 pts — actual 17 was 16.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="5" t="inlineStr">
         <is>
           <t>Cason Wallace</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="5" t="inlineStr">
         <is>
           <t>DET @ OKC</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D84" t="n">
+      <c r="D84" s="5" t="n">
         <v>7.5</v>
       </c>
+      <c r="E84" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Wallace scored 9 pts vs 7.5 line (+1.5), OVER hit by 1.5 pts. Wallace played 27 min (+3.5 vs L10 avg of 23.1) — 15% more than expected. Shooting was in line with averages: 44.4% FG (4/9, L10 avg 43.6%). Signals that called it correctly: Volume, HR L30, Context, H2H, FG Trend (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 18.1 pts — actual 9 was 9.1 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Wallace's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="5" t="inlineStr">
         <is>
           <t>Ausar Thompson</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="5" t="inlineStr">
         <is>
           <t>DET @ OKC</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D85" t="n">
+      <c r="D85" s="5" t="n">
         <v>11.5</v>
       </c>
+      <c r="E85" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Thompson scored 8 pts vs 11.5 line (-3.5), UNDER hit by 3.5 pts. Minutes were as expected: 26 played vs L10 avg 25.9. Shooting efficiency was hot: 60.0% FG (+12.6% vs L10 avg of 47.4%). 3/5 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (8/10 aligned). Counter-signals that were wrong: Trend, Min Trend. Projection model targeted 8.1 pts — actual 8 was 0.1 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J85" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="4" t="inlineStr">
         <is>
           <t>Chet Holmgren</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="4" t="inlineStr">
         <is>
           <t>DET @ OKC</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D86" t="n">
+      <c r="D86" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E86" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Holmgren scored 13 pts vs 15.5 line (-2.5), OVER missed by 2.5 pts. Minutes were as expected: 30 played vs L10 avg 28.8. Shooting was in line with averages: 54.5% FG (6/11, L10 avg 52.2%). Counter-signals that proved correct: HR L30, Trend, Defense, H2H. Signals that were wrong: Volume, HR L10, Context. Projection model targeted 18.5 pts — actual 13 was 5.5 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Holmgren's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="5" t="inlineStr">
         <is>
           <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="5" t="inlineStr">
         <is>
           <t>DET @ OKC</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D87" t="n">
+      <c r="D87" s="5" t="n">
         <v>29.5</v>
       </c>
+      <c r="E87" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Gilgeous-Alexander scored 47 pts vs 29.5 line (+17.5), OVER hit by 17.5 pts. Gilgeous-Alexander played 40 min (+6.8 vs L10 avg of 33.7) — 20% more than expected. Shooting was in line with averages: 63.2% FG (12/19, L10 avg 60.5%). Signals that called it correctly: Volume, HR L30, HR L10, Context, FG Trend (6/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 33.3 pts — actual 47 was 13.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Gilgeous-Alexander's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J87" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="3" t="inlineStr">
         <is>
           <t>Jalen Williams</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t>DET @ OKC</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D88" t="n">
+      <c r="D88" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E88" s="3" t="n"/>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="n"/>
+      <c r="H88" s="3" t="inlineStr"/>
+      <c r="I88" s="3" t="n"/>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="4" t="inlineStr">
         <is>
           <t>Caris LeVert</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>DET @ OKC</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D89" t="n">
+      <c r="D89" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E89" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — LeVert scored 10 pts vs 9.5 line (+0.5), UNDER missed by 0.5 pts. LeVert played 26 min (+6.8 vs L10 avg of 19.3) — 35% more than expected. Shooting was in line with averages: 36.4% FG (4/11, L10 avg 36.8%). Counter-signals that proved correct: Trend, H2H, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 9.0 pts — actual 10 was 1.0 pts close (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="4" t="inlineStr">
         <is>
           <t>Paul Reed</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="4" t="inlineStr">
         <is>
           <t>DET @ OKC</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D90" t="n">
+      <c r="D90" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E90" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Reed scored 21 pts vs 12.5 line (+8.5), UNDER missed by 8.5 pts. Reed played 34 min (+20.0 vs L10 avg of 14.1) — 142% more than expected. Shooting was in line with averages: 53.8% FG (7/13, L10 avg 56.1%). Counter-signals that proved correct: Trend, H2H. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 9.1 pts — actual 21 was 11.9 pts off (correct direction). Loss classification: BLOWOUT_EFFECT. Note: Game script invalidated the prop. Consider blowout probability when DET is involved.</t>
+        </is>
+      </c>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="4" t="inlineStr">
         <is>
           <t>Luguentz Dort</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="4" t="inlineStr">
         <is>
           <t>DET @ OKC</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C91" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D91" t="n">
+      <c r="D91" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E91" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Dort scored 2 pts vs 6.5 line (-4.5), OVER missed by 4.5 pts. Dort played 22 min (-3.1 vs L10 avg of 25.1) — 12% less than expected. Shooting was in line with averages: 25.0% FG (1/4, L10 avg 29.5%). Counter-signals that proved correct: HR L10, Trend, Defense, Pace. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 6.9 pts — actual 2 was 4.9 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Dort's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="5" t="inlineStr">
         <is>
           <t>Will Riley</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="5" t="inlineStr">
         <is>
           <t>WAS @ LAL</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C92" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D92" t="n">
+      <c r="D92" s="5" t="n">
         <v>13.5</v>
       </c>
+      <c r="E92" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H92" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Riley scored 20 pts vs 13.5 line (+6.5), OVER hit by 6.5 pts. Riley played 36 min (+4.8 vs L10 avg of 31.2) — 15% more than expected. Shooting was in line with averages: 42.1% FG (8/19, L10 avg 43.8%). Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (6/10 aligned). Counter-signals that were wrong: Defense, H2H, Pace. Projection model targeted 14.4 pts — actual 20 was 5.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Riley's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="5" t="inlineStr">
         <is>
           <t>Tre Johnson</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="5" t="inlineStr">
         <is>
           <t>WAS @ LAL</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C93" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D93" t="n">
+      <c r="D93" s="5" t="n">
         <v>10.5</v>
       </c>
+      <c r="E93" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Johnson scored 11 pts vs 10.5 line (+0.5), OVER hit by 0.5 pts. Minutes were as expected: 23 played vs L10 avg 22.9. Shooting efficiency was hot: 41.7% FG (+5.2% vs L10 avg of 36.5%). 5/12 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context (4/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 11.5 pts — actual 11 was 0.5 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Johnson in this role.</t>
+        </is>
+      </c>
+      <c r="I93" s="5" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J93" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t>Bilal Coulibaly</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="3" t="inlineStr">
         <is>
           <t>WAS @ LAL</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D94" t="n">
+      <c r="D94" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E94" s="3" t="n"/>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="n"/>
+      <c r="H94" s="3" t="inlineStr"/>
+      <c r="I94" s="3" t="n"/>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="5" t="inlineStr">
         <is>
           <t>Austin Reaves</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="5" t="inlineStr">
         <is>
           <t>WAS @ LAL</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C95" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D95" t="n">
+      <c r="D95" s="5" t="n">
         <v>29.5</v>
       </c>
+      <c r="E95" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Reaves scored 19 pts vs 29.5 line (-10.5), UNDER hit by 10.5 pts. Reaves played 27 min (-12.8 vs L10 avg of 40.0) — 32% less than expected. Shooting efficiency was cold: 36.4% FG (-11.6% vs L10 avg of 48.0%). 4/11 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context (4/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 16.0 pts — actual 19 was 3.0 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Reaves's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I95" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J95" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t>Luke Kennard</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>WAS @ LAL</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D96" t="n">
+      <c r="D96" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E96" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Kennard scored 19 pts vs 11.5 line (+7.5), UNDER missed by 7.5 pts. Minutes were as expected: 23 played vs L10 avg 20.3. Shooting efficiency was hot: 70.0% FG (+31.5% vs L10 avg of 38.5%). 7/10 from the field. Counter-signals that proved correct: Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 8.8 pts — actual 19 was 10.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="5" t="inlineStr">
         <is>
           <t>LeBron James</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="5" t="inlineStr">
         <is>
           <t>WAS @ LAL</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C97" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D97" t="n">
+      <c r="D97" s="5" t="n">
         <v>23.5</v>
       </c>
+      <c r="E97" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>WIN — James scored 21 pts vs 23.5 line (-2.5), UNDER hit by 2.5 pts. Minutes were as expected: 33 played vs L10 avg 35.7. Shooting efficiency was cold: 50.0% FG (-6.1% vs L10 avg of 56.1%). 8/16 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (6/10 aligned). Counter-signals that were wrong: Defense, Pace, FG Trend. Projection model targeted 18.0 pts — actual 21 was 3.0 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms James's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I97" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J97" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t>Deandre Ayton</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="4" t="inlineStr">
         <is>
           <t>WAS @ LAL</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D98" t="n">
+      <c r="D98" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E98" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Ayton scored 12 pts vs 14.5 line (-2.5), OVER missed by 2.5 pts. Ayton played 22 min (-6.2 vs L10 avg of 28.6) — 22% less than expected. Shooting efficiency was hot: 100.0% FG (+27.0% vs L10 avg of 73.0%). 5/5 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, Defense, Pace. Projection model targeted 19.0 pts — actual 12 was 7.0 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Ayton for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="3" t="inlineStr">
         <is>
           <t>Alex Sarr</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="3" t="inlineStr">
         <is>
           <t>WAS @ LAL</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C99" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D99" t="n">
+      <c r="D99" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E99" s="3" t="n"/>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="n"/>
+      <c r="H99" s="3" t="inlineStr"/>
+      <c r="I99" s="3" t="n"/>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="4" t="inlineStr">
         <is>
           <t>Rui Hachimura</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="4" t="inlineStr">
         <is>
           <t>WAS @ LAL</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C100" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D100" t="n">
+      <c r="D100" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E100" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Hachimura scored 14 pts vs 12.5 line (+1.5), UNDER missed by 1.5 pts. Minutes were as expected: 26 played vs L10 avg 25.2. Shooting efficiency was hot: 60.0% FG (+5.7% vs L10 avg of 54.3%). 6/10 from the field. Counter-signals that proved correct: Defense, H2H, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 8.5 pts — actual 14 was 5.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="5" t="inlineStr">
         <is>
           <t>Bronny James</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="5" t="inlineStr">
         <is>
           <t>WAS @ LAL</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C101" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D101" t="n">
+      <c r="D101" s="5" t="n">
         <v>6.5</v>
       </c>
+      <c r="E101" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>WIN — James scored 6 pts vs 6.5 line (-0.5), UNDER hit by 0.5 pts. James played 26 min (+18.0 vs L10 avg of 7.6) — 237% more than expected. Shooting efficiency was cold: 20.0% FG (-18.3% vs L10 avg of 38.3%). 2/10 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (6/10 aligned). Counter-signals that were wrong: Defense, Pace, FG Trend. Projection model targeted 2.7 pts — actual 6 was 3.3 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms James's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J101" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="5" t="inlineStr">
         <is>
           <t>Jake LaRavia</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B102" s="5" t="inlineStr">
         <is>
           <t>WAS @ LAL</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C102" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D102" t="n">
+      <c r="D102" s="5" t="n">
         <v>10.5</v>
+      </c>
+      <c r="E102" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H102" s="5" t="inlineStr">
+        <is>
+          <t>WIN — LaRavia scored 4 pts vs 10.5 line (-6.5), UNDER hit by 6.5 pts. LaRavia played 28 min (+9.1 vs L10 avg of 18.8) — 48% more than expected. Shooting efficiency was hot: 66.7% FG (+21.1% vs L10 avg of 45.6%). 2/3 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: Defense, Pace. Projection model targeted 4.0 pts — actual 4 was 0.0 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J102" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:07</t>
+        </is>
       </c>
     </row>
   </sheetData>
